--- a/XProject/Docs/Far_Cry_5_Fishing_Gantt_v2.xlsx
+++ b/XProject/Docs/Far_Cry_5_Fishing_Gantt_v2.xlsx
@@ -547,7 +547,7 @@
       <c r="J1" s="18" t="n"/>
     </row>
     <row r="2" ht="24" customHeight="1" s="17">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="30" t="inlineStr">
         <is>
           <t>依据 Notion 文档：《Far Cry 5 钓鱼小游戏 PRD（拆解）》</t>
         </is>
@@ -563,7 +563,7 @@
       <c r="J2" s="18" t="n"/>
     </row>
     <row r="3" ht="24" customHeight="1" s="17">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="30" t="inlineStr">
         <is>
           <t>规划假设：4 周冲刺，每周 5 个工作日，按 M1→M4 逐步交付，并纳入美术/音效占位与补齐</t>
         </is>
@@ -580,52 +580,52 @@
     </row>
     <row r="4" ht="24" customHeight="1" s="17"/>
     <row r="5" ht="24" customHeight="1" s="17">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="19" t="inlineStr">
         <is>
           <t>阶段</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" s="19" t="inlineStr">
         <is>
           <t>模块</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C5" s="19" t="inlineStr">
         <is>
           <t>主要工作项</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="D5" s="19" t="inlineStr">
         <is>
           <t>交付物</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="E5" s="19" t="inlineStr">
         <is>
           <t>负责人建议</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr">
+      <c r="F5" s="19" t="inlineStr">
         <is>
           <t>W1</t>
         </is>
       </c>
-      <c r="G5" s="4" t="inlineStr">
+      <c r="G5" s="19" t="inlineStr">
         <is>
           <t>W2</t>
         </is>
       </c>
-      <c r="H5" s="4" t="inlineStr">
+      <c r="H5" s="19" t="inlineStr">
         <is>
           <t>W3</t>
         </is>
       </c>
-      <c r="I5" s="4" t="inlineStr">
+      <c r="I5" s="19" t="inlineStr">
         <is>
           <t>W4</t>
         </is>
       </c>
-      <c r="J5" s="4" t="inlineStr">
+      <c r="J5" s="19" t="inlineStr">
         <is>
           <t>里程碑/备注</t>
         </is>
@@ -652,27 +652,27 @@
       </c>
     </row>
     <row r="6" ht="37.5" customHeight="1" s="17">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="A6" s="24" t="inlineStr">
         <is>
           <t>M1 基础闭环</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="30" t="inlineStr">
         <is>
           <t>基础交互</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C6" s="30" t="inlineStr">
         <is>
           <t>装备钓竿、抛竿、咬钩、遛鱼、上鱼状态机</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="D6" s="30" t="inlineStr">
         <is>
           <t>可玩钓鱼闭环 Demo</t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="E6" s="30" t="inlineStr">
         <is>
           <t>玩法程序</t>
         </is>
@@ -685,54 +685,54 @@
       <c r="G6" s="7" t="n"/>
       <c r="H6" s="7" t="n"/>
       <c r="I6" s="7" t="n"/>
-      <c r="J6" s="3" t="inlineStr">
+      <c r="J6" s="30" t="inlineStr">
         <is>
           <t>周末形成首次可玩版本</t>
         </is>
       </c>
       <c r="K6" s="20" t="inlineStr">
         <is>
-          <t>已完成</t>
+          <t>???</t>
         </is>
       </c>
       <c r="L6" s="21" t="inlineStr">
         <is>
-          <t>85%</t>
+          <t>95%</t>
         </is>
       </c>
       <c r="M6" s="21" t="inlineStr">
         <is>
-          <t>FishGamePresenter 已实现待命/抛竿/等待/遛鱼状态机、成功上鱼与失败提示；FishGameMainUI 已接入运行时。</t>
+          <t>FishGamePresenterV2 ?????/??/??/??/??/???????????????45m ???????? UI ???</t>
         </is>
       </c>
       <c r="N6" s="21" t="inlineStr">
         <is>
-          <t>继续把“装备钓竿”从 FishGame UI 演示推进到角色/武器入口。</t>
+          <t>?????????? FishGame UI ???????/????????????????</t>
         </is>
       </c>
     </row>
     <row r="7" ht="37.5" customHeight="1" s="17">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" s="24" t="inlineStr">
         <is>
           <t>M1 基础闭环</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="30" t="inlineStr">
         <is>
           <t>鱼与钓点</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" s="30" t="inlineStr">
         <is>
           <t>基础鱼 AI / 刷新 / 基础钓点配置 / 水域判定</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D7" s="30" t="inlineStr">
         <is>
           <t>基础钓点 1 处</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
+      <c r="E7" s="30" t="inlineStr">
         <is>
           <t>策划+程序</t>
         </is>
@@ -745,7 +745,7 @@
       <c r="G7" s="7" t="n"/>
       <c r="H7" s="7" t="n"/>
       <c r="I7" s="7" t="n"/>
-      <c r="J7" s="3" t="inlineStr">
+      <c r="J7" s="30" t="inlineStr">
         <is>
           <t>支持首钓</t>
         </is>
@@ -772,27 +772,27 @@
       </c>
     </row>
     <row r="8" ht="37.5" customHeight="1" s="17">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="A8" s="24" t="inlineStr">
         <is>
           <t>M1 基础闭环</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="30" t="inlineStr">
         <is>
           <t>工具接入</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" s="30" t="inlineStr">
         <is>
           <t>武器轮盘挂接钓竿、背包记录鱼</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D8" s="30" t="inlineStr">
         <is>
           <t>轮盘与库存可用</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="E8" s="30" t="inlineStr">
         <is>
           <t>客户端</t>
         </is>
@@ -805,54 +805,54 @@
       <c r="G8" s="7" t="n"/>
       <c r="H8" s="7" t="n"/>
       <c r="I8" s="7" t="n"/>
-      <c r="J8" s="3" t="inlineStr">
+      <c r="J8" s="30" t="inlineStr">
         <is>
           <t>流程可从主循环进入</t>
         </is>
       </c>
       <c r="K8" s="22" t="inlineStr">
         <is>
-          <t>部分完成</t>
+          <t>????</t>
         </is>
       </c>
       <c r="L8" s="21" t="inlineStr">
         <is>
-          <t>35%</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="M8" s="21" t="inlineStr">
         <is>
-          <t>FishGame 已注册为默认 Gameplay，且可与 TripleMerge 双向切换；鱼获只记录在 FishGame 内部列表。</t>
+          <t>FishGame ???? Gameplay ????? TripleMerge ?????FishGame ????????????? FishGame ????</t>
         </is>
       </c>
       <c r="N8" s="21" t="inlineStr">
         <is>
-          <t>补武器轮盘挂竿、正式背包/库存接入，避免停留在 UI 内部账本。</t>
+          <t>????????????/???????????????????</t>
         </is>
       </c>
     </row>
     <row r="9" ht="37.5" customHeight="1" s="17">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" s="24" t="inlineStr">
         <is>
           <t>M1 基础闭环</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="30" t="inlineStr">
         <is>
           <t>经济闭环</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C9" s="30" t="inlineStr">
         <is>
           <t>商贩出售鱼换钱、失败提示（断线/脱钩）</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="D9" s="30" t="inlineStr">
         <is>
           <t>售卖界面初版</t>
         </is>
       </c>
-      <c r="E9" s="3" t="inlineStr">
+      <c r="E9" s="30" t="inlineStr">
         <is>
           <t>客户端</t>
         </is>
@@ -865,54 +865,54 @@
       <c r="G9" s="7" t="n"/>
       <c r="H9" s="7" t="n"/>
       <c r="I9" s="7" t="n"/>
-      <c r="J9" s="3" t="inlineStr">
+      <c r="J9" s="30" t="inlineStr">
         <is>
           <t>形成上鱼→变现闭环</t>
         </is>
       </c>
       <c r="K9" s="22" t="inlineStr">
         <is>
-          <t>部分完成</t>
+          <t>????</t>
         </is>
       </c>
       <c r="L9" s="21" t="inlineStr">
         <is>
-          <t>30%</t>
+          <t>70%</t>
         </is>
       </c>
       <c r="M9" s="21" t="inlineStr">
         <is>
-          <t>断线/脱钩失败提示与“总价值”累计已实现，但未调用统一货币系统，也未见商贩售卖流程。</t>
+          <t>???????????Coin ??????????????????????????????????????</t>
         </is>
       </c>
       <c r="N9" s="21" t="inlineStr">
         <is>
-          <t>补卖鱼入口、商贩 UI、货币到账与失败后恢复链路。</t>
+          <t>??? UI/??????????????????????????</t>
         </is>
       </c>
     </row>
     <row r="10" ht="37.5" customHeight="1" s="17">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="A10" s="24" t="inlineStr">
         <is>
           <t>M2 成长系统</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" s="30" t="inlineStr">
         <is>
           <t>Perk 接入</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C10" s="30" t="inlineStr">
         <is>
           <t>Fisher King 接入，疲劳加速参数生效</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="D10" s="30" t="inlineStr">
         <is>
           <t>Perk 效果可验证</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="E10" s="30" t="inlineStr">
         <is>
           <t>玩法程序</t>
         </is>
@@ -925,7 +925,7 @@
       </c>
       <c r="H10" s="7" t="n"/>
       <c r="I10" s="7" t="n"/>
-      <c r="J10" s="3" t="inlineStr">
+      <c r="J10" s="30" t="inlineStr">
         <is>
           <t>成长逻辑贯通</t>
         </is>
@@ -952,27 +952,27 @@
       </c>
     </row>
     <row r="11" ht="37.5" customHeight="1" s="17">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="A11" s="24" t="inlineStr">
         <is>
           <t>M2 成长系统</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" s="30" t="inlineStr">
         <is>
           <t>鱼饵系统</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C11" s="30" t="inlineStr">
         <is>
           <t>5 种鱼饵数据、切换轮盘、未解锁置灰</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="D11" s="30" t="inlineStr">
         <is>
           <t>鱼饵轮盘</t>
         </is>
       </c>
-      <c r="E11" s="3" t="inlineStr">
+      <c r="E11" s="30" t="inlineStr">
         <is>
           <t>客户端+策划</t>
         </is>
@@ -985,54 +985,54 @@
       </c>
       <c r="H11" s="7" t="n"/>
       <c r="I11" s="7" t="n"/>
-      <c r="J11" s="3" t="inlineStr">
+      <c r="J11" s="30" t="inlineStr">
         <is>
           <t>有清晰解锁反馈</t>
         </is>
       </c>
       <c r="K11" s="22" t="inlineStr">
         <is>
-          <t>部分完成</t>
+          <t>????</t>
         </is>
       </c>
       <c r="L11" s="21" t="inlineStr">
         <is>
-          <t>45%</t>
+          <t>70%</t>
         </is>
       </c>
       <c r="M11" s="21" t="inlineStr">
         <is>
-          <t>5 种鱼饵数据、切换按钮与“未解锁，仅演示”文案已存在。</t>
+          <t>??? 5 ?????????????????????????????????????????????????</t>
         </is>
       </c>
       <c r="N11" s="21" t="inlineStr">
         <is>
-          <t>补轮盘表现、未解锁置灰和真实解锁状态，不要只停留在文案。</t>
+          <t>?????????????????????????? FishGame ???????</t>
         </is>
       </c>
     </row>
     <row r="12" ht="37.5" customHeight="1" s="17">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="A12" s="24" t="inlineStr">
         <is>
           <t>M2 成长系统</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B12" s="30" t="inlineStr">
         <is>
           <t>鱼种偏好</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C12" s="30" t="inlineStr">
         <is>
           <t>鱼饵-鱼种偏好规则与重鱼生成条件</t>
         </is>
       </c>
-      <c r="D12" s="3" t="inlineStr">
+      <c r="D12" s="30" t="inlineStr">
         <is>
           <t>Fish/Rod/Lure 数据表 v1</t>
         </is>
       </c>
-      <c r="E12" s="3" t="inlineStr">
+      <c r="E12" s="30" t="inlineStr">
         <is>
           <t>策划</t>
         </is>
@@ -1045,54 +1045,54 @@
       </c>
       <c r="H12" s="7" t="n"/>
       <c r="I12" s="7" t="n"/>
-      <c r="J12" s="3" t="inlineStr">
+      <c r="J12" s="30" t="inlineStr">
         <is>
           <t>为重鱼与纪录铺路</t>
         </is>
       </c>
       <c r="K12" s="22" t="inlineStr">
         <is>
-          <t>部分完成</t>
+          <t>????</t>
         </is>
       </c>
       <c r="L12" s="21" t="inlineStr">
         <is>
-          <t>35%</t>
+          <t>75%</t>
         </is>
       </c>
       <c r="M12" s="21" t="inlineStr">
         <is>
-          <t>鱼饵命中鱼种时权重×3 已实现，能体现基础偏好。</t>
+          <t>Fish/Rod/Lure/Distance/Global ????????????????????????????????????</t>
         </is>
       </c>
       <c r="N12" s="21" t="inlineStr">
         <is>
-          <t>补 Fish/Rod/Lure 数据表、重鱼生成条件和可配置验证入口。</t>
+          <t>???????????????????????????</t>
         </is>
       </c>
     </row>
     <row r="13" ht="37.5" customHeight="1" s="17">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="A13" s="24" t="inlineStr">
         <is>
           <t>M3 目标系统</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B13" s="30" t="inlineStr">
         <is>
           <t>Hard Spot</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="C13" s="30" t="inlineStr">
         <is>
           <t>Hard Fishing Spot 标记、难度规则、挑战鱼生成</t>
         </is>
       </c>
-      <c r="D13" s="3" t="inlineStr">
+      <c r="D13" s="30" t="inlineStr">
         <is>
           <t>硬钓点玩法可测</t>
         </is>
       </c>
-      <c r="E13" s="3" t="inlineStr">
+      <c r="E13" s="30" t="inlineStr">
         <is>
           <t>策划+程序</t>
         </is>
@@ -1105,7 +1105,7 @@
         </is>
       </c>
       <c r="I13" s="7" t="n"/>
-      <c r="J13" s="3" t="inlineStr">
+      <c r="J13" s="30" t="inlineStr">
         <is>
           <t>高阶挑战上线</t>
         </is>
@@ -1132,27 +1132,27 @@
       </c>
     </row>
     <row r="14" ht="37.5" customHeight="1" s="17">
-      <c r="A14" s="5" t="inlineStr">
+      <c r="A14" s="24" t="inlineStr">
         <is>
           <t>M3 目标系统</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B14" s="30" t="inlineStr">
         <is>
           <t>纪录板</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="C14" s="30" t="inlineStr">
         <is>
           <t>区域纪录计算、刷新逻辑、纪录板 UI</t>
         </is>
       </c>
-      <c r="D14" s="3" t="inlineStr">
+      <c r="D14" s="30" t="inlineStr">
         <is>
           <t>纪录板 UI v1</t>
         </is>
       </c>
-      <c r="E14" s="3" t="inlineStr">
+      <c r="E14" s="30" t="inlineStr">
         <is>
           <t>客户端</t>
         </is>
@@ -1165,7 +1165,7 @@
         </is>
       </c>
       <c r="I14" s="7" t="n"/>
-      <c r="J14" s="3" t="inlineStr">
+      <c r="J14" s="30" t="inlineStr">
         <is>
           <t>板子能更新</t>
         </is>
@@ -1192,27 +1192,27 @@
       </c>
     </row>
     <row r="15" ht="37.5" customHeight="1" s="17">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="A15" s="24" t="inlineStr">
         <is>
           <t>M3 目标系统</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B15" s="30" t="inlineStr">
         <is>
           <t>终极解锁</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="C15" s="30" t="inlineStr">
         <is>
           <t>Old Betsy 解锁条件判定与发放</t>
         </is>
       </c>
-      <c r="D15" s="3" t="inlineStr">
+      <c r="D15" s="30" t="inlineStr">
         <is>
           <t>终极鱼竿脚本</t>
         </is>
       </c>
-      <c r="E15" s="3" t="inlineStr">
+      <c r="E15" s="30" t="inlineStr">
         <is>
           <t>玩法程序</t>
         </is>
@@ -1225,7 +1225,7 @@
         </is>
       </c>
       <c r="I15" s="7" t="n"/>
-      <c r="J15" s="3" t="inlineStr">
+      <c r="J15" s="30" t="inlineStr">
         <is>
           <t>目标链闭环</t>
         </is>
@@ -1252,27 +1252,27 @@
       </c>
     </row>
     <row r="16" ht="37.5" customHeight="1" s="17">
-      <c r="A16" s="5" t="inlineStr">
+      <c r="A16" s="24" t="inlineStr">
         <is>
           <t>横向支持</t>
         </is>
       </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B16" s="30" t="inlineStr">
         <is>
           <t>角色与道具占位</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
+      <c r="C16" s="30" t="inlineStr">
         <is>
           <t>R15 角色沿用、基础钓竿/浮漂/鱼线 Beam 占位接入，确保第三人称演示成立</t>
         </is>
       </c>
-      <c r="D16" s="3" t="inlineStr">
+      <c r="D16" s="30" t="inlineStr">
         <is>
           <t>可演示角色钓鱼动作占位版</t>
         </is>
       </c>
-      <c r="E16" s="3" t="inlineStr">
+      <c r="E16" s="30" t="inlineStr">
         <is>
           <t>客户端+技术美术</t>
         </is>
@@ -1289,54 +1289,54 @@
       </c>
       <c r="H16" s="9" t="n"/>
       <c r="I16" s="7" t="n"/>
-      <c r="J16" s="3" t="inlineStr">
+      <c r="J16" s="30" t="inlineStr">
         <is>
           <t>先保证“能看懂、能演示”</t>
         </is>
       </c>
       <c r="K16" s="22" t="inlineStr">
         <is>
-          <t>部分完成</t>
+          <t>????</t>
         </is>
       </c>
       <c r="L16" s="21" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>30%</t>
         </is>
       </c>
       <c r="M16" s="21" t="inlineStr">
         <is>
-          <t>FishGame UI 已可运行并能从主循环进入。</t>
+          <t>FishGame UI ?????????????????????????/??/?? Beam ??????????</t>
         </is>
       </c>
       <c r="N16" s="21" t="inlineStr">
         <is>
-          <t>缺第三人称角色动作占位、基础钓竿/浮漂/鱼线 Beam 等道具接入。</t>
+          <t>????????????????????????????</t>
         </is>
       </c>
     </row>
     <row r="17" ht="37.5" customHeight="1" s="17">
-      <c r="A17" s="5" t="inlineStr">
+      <c r="A17" s="24" t="inlineStr">
         <is>
           <t>横向支持</t>
         </is>
       </c>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="B17" s="30" t="inlineStr">
         <is>
           <t>动画与手感反馈</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
+      <c r="C17" s="30" t="inlineStr">
         <is>
           <t>装备/抛竿/等待/收线/上鱼/失败动作占位，配合 whoosh、bite、reel、fail 等 P0 音效接入</t>
         </is>
       </c>
-      <c r="D17" s="3" t="inlineStr">
+      <c r="D17" s="30" t="inlineStr">
         <is>
           <t>动画/SFX 占位包 v1</t>
         </is>
       </c>
-      <c r="E17" s="3" t="inlineStr">
+      <c r="E17" s="30" t="inlineStr">
         <is>
           <t>客户端+音频</t>
         </is>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="H17" s="9" t="n"/>
       <c r="I17" s="7" t="n"/>
-      <c r="J17" s="3" t="inlineStr">
+      <c r="J17" s="30" t="inlineStr">
         <is>
           <t>首钓体验不再像木偶钓空气</t>
         </is>
@@ -1380,27 +1380,27 @@
       </c>
     </row>
     <row r="18" ht="37.5" customHeight="1" s="17">
-      <c r="A18" s="5" t="inlineStr">
+      <c r="A18" s="24" t="inlineStr">
         <is>
           <t>横向支持</t>
         </is>
       </c>
-      <c r="B18" s="3" t="inlineStr">
+      <c r="B18" s="30" t="inlineStr">
         <is>
           <t>鱼/UI 素材</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr">
+      <c r="C18" s="30" t="inlineStr">
         <is>
           <t>MVP 先做 4-6 种鱼模型或占位、鱼与鱼饵图标、咬钩/拉力/成功失败提示 UI</t>
         </is>
       </c>
-      <c r="D18" s="3" t="inlineStr">
+      <c r="D18" s="30" t="inlineStr">
         <is>
           <t>鱼/UI 素材包 v1</t>
         </is>
       </c>
-      <c r="E18" s="3" t="inlineStr">
+      <c r="E18" s="30" t="inlineStr">
         <is>
           <t>UI+美术</t>
         </is>
@@ -1417,54 +1417,54 @@
         </is>
       </c>
       <c r="I18" s="7" t="n"/>
-      <c r="J18" s="3" t="inlineStr">
+      <c r="J18" s="30" t="inlineStr">
         <is>
           <t>第2周先满足成长演示，第3周补全目标展示</t>
         </is>
       </c>
       <c r="K18" s="22" t="inlineStr">
         <is>
-          <t>部分完成</t>
+          <t>????</t>
         </is>
       </c>
       <c r="L18" s="21" t="inlineStr">
         <is>
-          <t>35%</t>
+          <t>45%</t>
         </is>
       </c>
       <c r="M18" s="21" t="inlineStr">
         <is>
-          <t>FishGame UI 预制体已完成，12 种鱼数据已定义。</t>
+          <t>FishGame UI ???????12 ??? 5 ?????????????/??/????????</t>
         </is>
       </c>
       <c r="N18" s="21" t="inlineStr">
         <is>
-          <t>缺 4-6 种可区分鱼模型或图标、鱼饵图标，以及咬钩/拉力/成功失败的素材化表现。</t>
+          <t>? 4-6 ?????????????????????????/??/???????</t>
         </is>
       </c>
     </row>
     <row r="19" ht="37.5" customHeight="1" s="17">
-      <c r="A19" s="5" t="inlineStr">
+      <c r="A19" s="24" t="inlineStr">
         <is>
           <t>横向支持</t>
         </is>
       </c>
-      <c r="B19" s="3" t="inlineStr">
+      <c r="B19" s="30" t="inlineStr">
         <is>
           <t>场景/VFX/纪录板</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr">
+      <c r="C19" s="30" t="inlineStr">
         <is>
           <t>水花/气泡/鱼跃提示、基础钓点场景件、商贩摊位、纪录板 UI 视觉稿与实现支持</t>
         </is>
       </c>
-      <c r="D19" s="3" t="inlineStr">
+      <c r="D19" s="30" t="inlineStr">
         <is>
           <t>钓点与纪录板表现 v1</t>
         </is>
       </c>
-      <c r="E19" s="3" t="inlineStr">
+      <c r="E19" s="30" t="inlineStr">
         <is>
           <t>美术+UI</t>
         </is>
@@ -1477,7 +1477,7 @@
         </is>
       </c>
       <c r="I19" s="7" t="n"/>
-      <c r="J19" s="3" t="inlineStr">
+      <c r="J19" s="30" t="inlineStr">
         <is>
           <t>支撑 Hard Spot 与纪录系统可读性</t>
         </is>
@@ -1504,27 +1504,27 @@
       </c>
     </row>
     <row r="20" ht="37.5" customHeight="1" s="17">
-      <c r="A20" s="5" t="inlineStr">
+      <c r="A20" s="24" t="inlineStr">
         <is>
           <t>横向支持</t>
         </is>
       </c>
-      <c r="B20" s="3" t="inlineStr">
+      <c r="B20" s="30" t="inlineStr">
         <is>
           <t>风格统一与素材清理</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr">
+      <c r="C20" s="30" t="inlineStr">
         <is>
           <t>补齐 12 种鱼展示、4 档钓竿差异化、免费素材安全检查、性能与体素风统一、P1 音效补强</t>
         </is>
       </c>
-      <c r="D20" s="3" t="inlineStr">
+      <c r="D20" s="30" t="inlineStr">
         <is>
           <t>美术音频整合包 v2</t>
         </is>
       </c>
-      <c r="E20" s="3" t="inlineStr">
+      <c r="E20" s="30" t="inlineStr">
         <is>
           <t>美术+客户端</t>
         </is>
@@ -1537,7 +1537,7 @@
           <t>■</t>
         </is>
       </c>
-      <c r="J20" s="3" t="inlineStr">
+      <c r="J20" s="30" t="inlineStr">
         <is>
           <t>上线前解决“功能有了但卖相很糙”问题</t>
         </is>
@@ -1564,7 +1564,7 @@
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1" s="17">
-      <c r="A21" s="5" t="inlineStr">
+      <c r="A21" s="24" t="inlineStr">
         <is>
           <t>M4 平衡打磨</t>
         </is>
@@ -1592,27 +1592,27 @@
       <c r="N21" s="24" t="n"/>
     </row>
     <row r="22" ht="15.75" customHeight="1" s="17">
-      <c r="A22" s="5" t="inlineStr">
+      <c r="A22" s="24" t="inlineStr">
         <is>
           <t>M4 平衡打磨</t>
         </is>
       </c>
-      <c r="B22" s="3" t="inlineStr">
+      <c r="B22" s="30" t="inlineStr">
         <is>
           <t>引导反馈</t>
         </is>
       </c>
-      <c r="C22" s="3" t="inlineStr">
+      <c r="C22" s="30" t="inlineStr">
         <is>
           <t>新手引导、提示文案、失败原因可读性优化</t>
         </is>
       </c>
-      <c r="D22" s="3" t="inlineStr">
+      <c r="D22" s="30" t="inlineStr">
         <is>
           <t>引导文案与提示版</t>
         </is>
       </c>
-      <c r="E22" s="3" t="inlineStr">
+      <c r="E22" s="30" t="inlineStr">
         <is>
           <t>策划+客户端</t>
         </is>
@@ -1625,54 +1625,54 @@
           <t>■</t>
         </is>
       </c>
-      <c r="J22" s="3" t="inlineStr">
+      <c r="J22" s="30" t="inlineStr">
         <is>
           <t>首钓学习成本下降</t>
         </is>
       </c>
       <c r="K22" s="22" t="inlineStr">
         <is>
-          <t>部分完成</t>
+          <t>????</t>
         </is>
       </c>
       <c r="L22" s="21" t="inlineStr">
         <is>
-          <t>30%</t>
+          <t>40%</t>
         </is>
       </c>
       <c r="M22" s="21" t="inlineStr">
         <is>
-          <t>已有基础提示文案、失败提示和操作说明，但没有正式新手引导系统。</t>
+          <t>??????????????????/????????????????????????</t>
         </is>
       </c>
       <c r="N22" s="21" t="inlineStr">
         <is>
-          <t>补首钓引导流程、失败原因分层提示与边界场景文案。</t>
+          <t>????????????????????????</t>
         </is>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1" s="17">
-      <c r="A23" s="5" t="inlineStr">
+      <c r="A23" s="24" t="inlineStr">
         <is>
           <t>M4 平衡打磨</t>
         </is>
       </c>
-      <c r="B23" s="3" t="inlineStr">
+      <c r="B23" s="30" t="inlineStr">
         <is>
           <t>埋点测试</t>
         </is>
       </c>
-      <c r="C23" s="3" t="inlineStr">
+      <c r="C23" s="30" t="inlineStr">
         <is>
           <t>埋点全量接入、边界场景测试、回归修复</t>
         </is>
       </c>
-      <c r="D23" s="3" t="inlineStr">
+      <c r="D23" s="30" t="inlineStr">
         <is>
           <t>测试报告+埋点验证</t>
         </is>
       </c>
-      <c r="E23" s="3" t="inlineStr">
+      <c r="E23" s="30" t="inlineStr">
         <is>
           <t>测试+程序</t>
         </is>
@@ -1685,7 +1685,7 @@
           <t>■</t>
         </is>
       </c>
-      <c r="J23" s="3" t="inlineStr">
+      <c r="J23" s="30" t="inlineStr">
         <is>
           <t>达到上线质量门槛</t>
         </is>
@@ -1714,7 +1714,7 @@
     <row r="24" ht="15.75" customHeight="1" s="17"/>
     <row r="25" ht="15.75" customHeight="1" s="17"/>
     <row r="26" ht="15.75" customHeight="1" s="17">
-      <c r="A26" s="11" t="inlineStr">
+      <c r="A26" s="25" t="inlineStr">
         <is>
           <t>里程碑定义</t>
         </is>
@@ -1742,116 +1742,116 @@
       <c r="N26" s="25" t="n"/>
     </row>
     <row r="27" ht="15.75" customHeight="1" s="17">
-      <c r="A27" s="5" t="inlineStr">
+      <c r="A27" s="24" t="inlineStr">
         <is>
           <t>M1</t>
         </is>
       </c>
-      <c r="B27" s="5" t="inlineStr">
+      <c r="B27" s="24" t="inlineStr">
         <is>
           <t>基础钓鱼闭环</t>
         </is>
       </c>
-      <c r="C27" s="3" t="inlineStr">
+      <c r="C27" s="30" t="inlineStr">
         <is>
           <t>从装备钓竿到成功上鱼并可出售</t>
         </is>
       </c>
-      <c r="D27" s="13" t="n"/>
-      <c r="E27" s="13" t="n"/>
-      <c r="F27" s="13" t="n"/>
-      <c r="G27" s="13" t="n"/>
-      <c r="H27" s="13" t="n"/>
-      <c r="I27" s="13" t="n"/>
-      <c r="J27" s="13" t="n"/>
+      <c r="D27" s="27" t="n"/>
+      <c r="E27" s="27" t="n"/>
+      <c r="F27" s="27" t="n"/>
+      <c r="G27" s="27" t="n"/>
+      <c r="H27" s="27" t="n"/>
+      <c r="I27" s="27" t="n"/>
+      <c r="J27" s="27" t="n"/>
       <c r="K27" s="26" t="inlineStr">
         <is>
-          <t>部分完成</t>
+          <t>????</t>
         </is>
       </c>
       <c r="L27" s="27" t="inlineStr">
         <is>
-          <t>60%</t>
+          <t>75%</t>
         </is>
       </c>
       <c r="M27" s="27" t="inlineStr">
         <is>
-          <t>已能进入钓鱼玩法并成功上鱼，但“可出售”尚未落到现有货币/商店链路。</t>
+          <t>?????????????????????? Coin???????????????????????</t>
         </is>
       </c>
       <c r="N27" s="27" t="inlineStr">
         <is>
-          <t>完成卖鱼与货币链路后再视为 M1 真正闭环。</t>
+          <t>????????????????????? M1 ?????</t>
         </is>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1" s="17">
-      <c r="A28" s="5" t="inlineStr">
+      <c r="A28" s="24" t="inlineStr">
         <is>
           <t>M2</t>
         </is>
       </c>
-      <c r="B28" s="5" t="inlineStr">
+      <c r="B28" s="24" t="inlineStr">
         <is>
           <t>成长系统</t>
         </is>
       </c>
-      <c r="C28" s="3" t="inlineStr">
+      <c r="C28" s="30" t="inlineStr">
         <is>
           <t>Perk、鱼饵、重鱼条件全部贯通</t>
         </is>
       </c>
-      <c r="D28" s="13" t="n"/>
-      <c r="E28" s="13" t="n"/>
-      <c r="F28" s="13" t="n"/>
-      <c r="G28" s="13" t="n"/>
-      <c r="H28" s="13" t="n"/>
-      <c r="I28" s="13" t="n"/>
-      <c r="J28" s="13" t="n"/>
+      <c r="D28" s="27" t="n"/>
+      <c r="E28" s="27" t="n"/>
+      <c r="F28" s="27" t="n"/>
+      <c r="G28" s="27" t="n"/>
+      <c r="H28" s="27" t="n"/>
+      <c r="I28" s="27" t="n"/>
+      <c r="J28" s="27" t="n"/>
       <c r="K28" s="26" t="inlineStr">
         <is>
-          <t>部分完成</t>
+          <t>????</t>
         </is>
       </c>
       <c r="L28" s="27" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>45%</t>
         </is>
       </c>
       <c r="M28" s="27" t="inlineStr">
         <is>
-          <t>鱼饵与鱼种偏好已有演示逻辑。</t>
+          <t>????????????????????????????</t>
         </is>
       </c>
       <c r="N28" s="27" t="inlineStr">
         <is>
-          <t>Perk、重鱼条件与数据表仍需落地，当前未达到里程碑口径。</t>
+          <t>Perk??????????????????????????????</t>
         </is>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1" s="17">
-      <c r="A29" s="5" t="inlineStr">
+      <c r="A29" s="24" t="inlineStr">
         <is>
           <t>M3</t>
         </is>
       </c>
-      <c r="B29" s="5" t="inlineStr">
+      <c r="B29" s="24" t="inlineStr">
         <is>
           <t>目标系统</t>
         </is>
       </c>
-      <c r="C29" s="3" t="inlineStr">
+      <c r="C29" s="30" t="inlineStr">
         <is>
           <t>Hard Spot、纪录板、Old Betsy 解锁完成</t>
         </is>
       </c>
-      <c r="D29" s="13" t="n"/>
-      <c r="E29" s="13" t="n"/>
-      <c r="F29" s="13" t="n"/>
-      <c r="G29" s="13" t="n"/>
-      <c r="H29" s="13" t="n"/>
-      <c r="I29" s="13" t="n"/>
-      <c r="J29" s="13" t="n"/>
+      <c r="D29" s="27" t="n"/>
+      <c r="E29" s="27" t="n"/>
+      <c r="F29" s="27" t="n"/>
+      <c r="G29" s="27" t="n"/>
+      <c r="H29" s="27" t="n"/>
+      <c r="I29" s="27" t="n"/>
+      <c r="J29" s="27" t="n"/>
       <c r="K29" s="28" t="inlineStr">
         <is>
           <t>未发现实现</t>
@@ -1874,28 +1874,28 @@
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1" s="17">
-      <c r="A30" s="5" t="inlineStr">
+      <c r="A30" s="24" t="inlineStr">
         <is>
           <t>M4</t>
         </is>
       </c>
-      <c r="B30" s="5" t="inlineStr">
+      <c r="B30" s="24" t="inlineStr">
         <is>
           <t>平衡与打磨</t>
         </is>
       </c>
-      <c r="C30" s="3" t="inlineStr">
+      <c r="C30" s="30" t="inlineStr">
         <is>
           <t>埋点、边界、引导、数值与测试回归完成</t>
         </is>
       </c>
-      <c r="D30" s="13" t="n"/>
-      <c r="E30" s="13" t="n"/>
-      <c r="F30" s="13" t="n"/>
-      <c r="G30" s="13" t="n"/>
-      <c r="H30" s="13" t="n"/>
-      <c r="I30" s="13" t="n"/>
-      <c r="J30" s="13" t="n"/>
+      <c r="D30" s="27" t="n"/>
+      <c r="E30" s="27" t="n"/>
+      <c r="F30" s="27" t="n"/>
+      <c r="G30" s="27" t="n"/>
+      <c r="H30" s="27" t="n"/>
+      <c r="I30" s="27" t="n"/>
+      <c r="J30" s="27" t="n"/>
       <c r="K30" s="28" t="inlineStr">
         <is>
           <t>未发现实现</t>
@@ -2925,7 +2925,7 @@
       <c r="B1" s="18" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="30" t="inlineStr">
         <is>
           <t>口径：必须能演示、能复现、能判定通过/不通过，避免那种“感觉差不多”式验收。</t>
         </is>
@@ -2936,27 +2936,27 @@
       <c r="E2" s="18" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="19" t="inlineStr">
         <is>
           <t>周次</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" s="19" t="inlineStr">
         <is>
           <t>验收主题</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C4" s="19" t="inlineStr">
         <is>
           <t>验收标准</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="D4" s="19" t="inlineStr">
         <is>
           <t>演示场景</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="E4" s="19" t="inlineStr">
         <is>
           <t>失败判定</t>
         </is>
@@ -2968,12 +2968,12 @@
           <t>第1周</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="30" t="inlineStr">
         <is>
           <t>M1 基础钓鱼闭环</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C5" s="30" t="inlineStr">
         <is>
           <t>1) 新档已解锁钓竿后，30 秒内可完成 1 次成功钓鱼。
 2) 玩家可在武器轮盘装备钓竿并在可钓水域正常抛竿。
@@ -2983,12 +2983,12 @@
 6) 第三人称下至少具备“可读”的钓鱼动作与 P0 音效反馈，不允许全静态无反馈演示。</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D5" s="30" t="inlineStr">
         <is>
           <t>新档进入基础钓点，展示第三人称装备/抛竿/咬钩/上鱼反馈，先成功钓 1 条鱼，再故意操作失误触发 1 次失败，最后出售鱼。</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="E5" s="30" t="inlineStr">
         <is>
           <t>任一核心链路中断；库存/金钱不同步；失败后无反馈或反馈错误。</t>
         </is>
@@ -3000,12 +3000,12 @@
           <t>第2周</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="30" t="inlineStr">
         <is>
           <t>M2 成长与鱼饵</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C6" s="30" t="inlineStr">
         <is>
           <t>1) Fisher King perk 解锁后立即生效，遛鱼耗时有可感知下降。
 2) 5 种鱼饵可见，可切换，未解锁状态正确置灰。
@@ -3014,12 +3014,12 @@
 5) MVP 鱼/UI 素材已接入，至少 4-6 种鱼在图标或模型层面可区分。</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="D6" s="30" t="inlineStr">
         <is>
           <t>演示 perk 解锁前后同种鱼的遛鱼时间差；切换至少 3 种鱼饵并验证目标鱼偏好差异，同时确认鱼/UI 资产已能区分主要内容。</t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="E6" s="30" t="inlineStr">
         <is>
           <t>Perk 不生效；鱼饵无法切换；偏好规则与配置不一致；重鱼条件不可复现。</t>
         </is>
@@ -3031,12 +3031,12 @@
           <t>第3周</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="30" t="inlineStr">
         <is>
           <t>M3 目标系统</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" s="30" t="inlineStr">
         <is>
           <t>1) Hard Fishing Spot 可稳定触发挑战鱼规则。
 2) 破纪录后区域纪录板立即更新。
@@ -3045,12 +3045,12 @@
 5) 鱼跃提示、纪录板 UI、基础钓点场景件已到位，目标系统具备足够可读性。</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D7" s="30" t="inlineStr">
         <is>
           <t>在指定硬钓点完成 1 次挑战鱼捕获，刷新 1 条纪录，并展示纪录板 UI、鱼跃提示和 Old Betsy 领取。</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
+      <c r="E7" s="30" t="inlineStr">
         <is>
           <t>硬钓点不稳定；纪录不刷新或显示错误；终极鱼竿条件判定错误；玩家无进度反馈。</t>
         </is>
@@ -3062,12 +3062,12 @@
           <t>第4周</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="30" t="inlineStr">
         <is>
           <t>M4 平衡与上线质量</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" s="30" t="inlineStr">
         <is>
           <t>1) 核心埋点事件可正常上报并验证字段完整。
 2) 关键测试用例全部通过，无阻塞级 bug。
@@ -3077,12 +3077,12 @@
 6) 免费素材已完成安全清理与性能检查，视觉风格和音效完成基础统一。</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D8" s="30" t="inlineStr">
         <is>
           <t>跑完整新手流程与 1 轮回归用例，检查日志/埋点；对比钓鱼收益与其他经济来源，并抽查免费模型/音效的安全和性能。</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="E8" s="30" t="inlineStr">
         <is>
           <t>埋点缺失；存在阻塞 bug；新手首钓频繁失败；经济失衡；边界场景误导玩家。</t>
         </is>
@@ -4100,60 +4100,60 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" s="24" t="inlineStr">
         <is>
           <t>项目节奏</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="30" t="inlineStr">
         <is>
           <t>4 周，建议每周预留 0.5 天缓冲</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="24" t="inlineStr">
         <is>
           <t>关键依赖</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="30" t="inlineStr">
         <is>
           <t>武器轮盘、背包/库存、商店系统、Perk 系统、UI 资源支持、免费素材筛选与清理流程</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" s="24" t="inlineStr">
         <is>
           <t>资源建议</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="30" t="inlineStr">
         <is>
           <t>1 名玩法程序 + 1 名客户端/UI + 1 名策划/数值 + 测试支持；美术/音频可由兼职或免费素材占位补足</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="A6" s="24" t="inlineStr">
         <is>
           <t>风险提示</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="30" t="inlineStr">
         <is>
           <t>若第2周素材接入拖慢玩法，可先用占位模型/纯文字 UI 保证功能验收；免费模型导入必须清理未知脚本</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" s="24" t="inlineStr">
         <is>
           <t>来源</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="30" t="inlineStr">
         <is>
           <t>https://www.notion.so/c54ed9a1d3014e379ed1ae15d496527f （2026-03-21 更新版，含美术与音效素材清单）</t>
         </is>
@@ -6443,13 +6443,27 @@
           <t>Far Cry 5 钓鱼小游戏 - 当前进度跟踪</t>
         </is>
       </c>
+      <c r="B1" s="18" t="n"/>
+      <c r="C1" s="18" t="n"/>
+      <c r="D1" s="18" t="n"/>
+      <c r="E1" s="18" t="n"/>
+      <c r="F1" s="18" t="n"/>
+      <c r="G1" s="18" t="n"/>
+      <c r="H1" s="18" t="n"/>
     </row>
     <row r="2" ht="36" customHeight="1" s="17">
       <c r="A2" s="30" t="inlineStr">
         <is>
-          <t>更新日期：2026-03-26；评估口径：仅以当前仓库内已接入的代码与资源为准，不按 PRD 文案视为完成。</t>
-        </is>
-      </c>
+          <t>?????2026-03-27??????????????????????????? PRD ???????</t>
+        </is>
+      </c>
+      <c r="B2" s="18" t="n"/>
+      <c r="C2" s="18" t="n"/>
+      <c r="D2" s="18" t="n"/>
+      <c r="E2" s="18" t="n"/>
+      <c r="F2" s="18" t="n"/>
+      <c r="G2" s="18" t="n"/>
+      <c r="H2" s="18" t="n"/>
     </row>
     <row r="3" ht="24" customHeight="1" s="17"/>
     <row r="4" ht="24" customHeight="1" s="17">
@@ -6496,7 +6510,7 @@
       </c>
       <c r="E5" s="21" t="inlineStr">
         <is>
-          <t>Demo 已形成，但库存/卖鱼/货币仍未接正式系统。</t>
+          <t>???????????/??/Coin/?????????????????????????</t>
         </is>
       </c>
     </row>
@@ -6517,7 +6531,7 @@
       </c>
       <c r="E6" s="21" t="inlineStr">
         <is>
-          <t>鱼饵与偏好有演示，Perk 与重鱼未落地。</t>
+          <t>?????????????????????Perk ?????????</t>
         </is>
       </c>
     </row>
@@ -6580,24 +6594,24 @@
       </c>
       <c r="E9" s="21" t="inlineStr">
         <is>
-          <t>只有基础提示文案，埋点与测试尚未开始。</t>
+          <t>??????????????????????????????</t>
         </is>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" s="17"/>
     <row r="11" ht="24" customHeight="1" s="17">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="A11" s="24" t="inlineStr">
         <is>
           <t>持续跟进明细</t>
         </is>
       </c>
-      <c r="B11" s="5" t="n"/>
-      <c r="C11" s="5" t="n"/>
-      <c r="D11" s="5" t="n"/>
-      <c r="E11" s="5" t="n"/>
-      <c r="F11" s="5" t="n"/>
-      <c r="G11" s="5" t="n"/>
-      <c r="H11" s="5" t="n"/>
+      <c r="B11" s="24" t="n"/>
+      <c r="C11" s="24" t="n"/>
+      <c r="D11" s="24" t="n"/>
+      <c r="E11" s="24" t="n"/>
+      <c r="F11" s="24" t="n"/>
+      <c r="G11" s="24" t="n"/>
+      <c r="H11" s="24" t="n"/>
     </row>
     <row r="12" ht="24" customHeight="1" s="17">
       <c r="A12" s="19" t="inlineStr">
@@ -6654,17 +6668,17 @@
       </c>
       <c r="C13" s="33" t="inlineStr">
         <is>
-          <t>已完成</t>
+          <t>???</t>
         </is>
       </c>
       <c r="D13" s="32" t="inlineStr">
         <is>
-          <t>85%</t>
+          <t>95%</t>
         </is>
       </c>
       <c r="E13" s="21" t="inlineStr">
         <is>
-          <t>FishGamePresenter 已实现待命/抛竿/等待/遛鱼状态机、成功上鱼与失败提示；FishGameMainUI 已接入运行时。</t>
+          <t>FishGamePresenterV2 ?????/??/??/??/??/???????????????45m ???????? UI ???</t>
         </is>
       </c>
       <c r="F13" s="21" t="inlineStr">
@@ -6674,12 +6688,12 @@
       </c>
       <c r="G13" s="21" t="inlineStr">
         <is>
-          <t>继续把“装备钓竿”从 FishGame UI 演示推进到角色/武器入口。</t>
+          <t>?????????? FishGame UI ???????/?????</t>
         </is>
       </c>
       <c r="H13" s="21" t="inlineStr">
         <is>
-          <t>把钓鱼入口从 UI 演示推进到角色/武器装备链。</t>
+          <t>?????? UI ???????/???????????????</t>
         </is>
       </c>
     </row>
@@ -6738,17 +6752,17 @@
       </c>
       <c r="C15" s="34" t="inlineStr">
         <is>
-          <t>部分完成</t>
+          <t>????</t>
         </is>
       </c>
       <c r="D15" s="32" t="inlineStr">
         <is>
-          <t>35%</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="E15" s="21" t="inlineStr">
         <is>
-          <t>FishGame 已注册为默认 Gameplay，且可与 TripleMerge 双向切换；鱼获只记录在 FishGame 内部列表。</t>
+          <t>FishGame ???? Gameplay ????? TripleMerge ?????FishGame ????????????? FishGame ????</t>
         </is>
       </c>
       <c r="F15" s="21" t="inlineStr">
@@ -6758,12 +6772,12 @@
       </c>
       <c r="G15" s="21" t="inlineStr">
         <is>
-          <t>补武器轮盘挂竿、正式背包/库存接入，避免停留在 UI 内部账本。</t>
+          <t>????????????/????????????????</t>
         </is>
       </c>
       <c r="H15" s="21" t="inlineStr">
         <is>
-          <t>接正式背包/库存，再补武器轮盘。</t>
+          <t>??????/??????????</t>
         </is>
       </c>
     </row>
@@ -6780,17 +6794,17 @@
       </c>
       <c r="C16" s="34" t="inlineStr">
         <is>
-          <t>部分完成</t>
+          <t>????</t>
         </is>
       </c>
       <c r="D16" s="32" t="inlineStr">
         <is>
-          <t>30%</t>
+          <t>70%</t>
         </is>
       </c>
       <c r="E16" s="21" t="inlineStr">
         <is>
-          <t>断线/脱钩失败提示与“总价值”累计已实现，但未调用统一货币系统，也未见商贩售卖流程。</t>
+          <t>???????????Coin ??????????????????????????????????????</t>
         </is>
       </c>
       <c r="F16" s="21" t="inlineStr">
@@ -6800,12 +6814,12 @@
       </c>
       <c r="G16" s="21" t="inlineStr">
         <is>
-          <t>补卖鱼入口、商贩 UI、货币到账与失败后恢复链路。</t>
+          <t>??? UI??????????????????????</t>
         </is>
       </c>
       <c r="H16" s="21" t="inlineStr">
         <is>
-          <t>做商贩卖鱼与 CurrencyModel 入账。</t>
+          <t>????????????????</t>
         </is>
       </c>
     </row>
@@ -6864,17 +6878,17 @@
       </c>
       <c r="C18" s="34" t="inlineStr">
         <is>
-          <t>部分完成</t>
+          <t>????</t>
         </is>
       </c>
       <c r="D18" s="32" t="inlineStr">
         <is>
-          <t>45%</t>
+          <t>70%</t>
         </is>
       </c>
       <c r="E18" s="21" t="inlineStr">
         <is>
-          <t>5 种鱼饵数据、切换按钮与“未解锁，仅演示”文案已存在。</t>
+          <t>??? 5 ??????????????????????????????????????</t>
         </is>
       </c>
       <c r="F18" s="21" t="inlineStr">
@@ -6884,12 +6898,12 @@
       </c>
       <c r="G18" s="21" t="inlineStr">
         <is>
-          <t>补轮盘表现、未解锁置灰和真实解锁状态，不要只停留在文案。</t>
+          <t>????????????????????</t>
         </is>
       </c>
       <c r="H18" s="21" t="inlineStr">
         <is>
-          <t>做未解锁置灰和解锁来源。</t>
+          <t>???????????????????</t>
         </is>
       </c>
     </row>
@@ -6906,17 +6920,17 @@
       </c>
       <c r="C19" s="34" t="inlineStr">
         <is>
-          <t>部分完成</t>
+          <t>????</t>
         </is>
       </c>
       <c r="D19" s="32" t="inlineStr">
         <is>
-          <t>35%</t>
+          <t>75%</t>
         </is>
       </c>
       <c r="E19" s="21" t="inlineStr">
         <is>
-          <t>鱼饵命中鱼种时权重×3 已实现，能体现基础偏好。</t>
+          <t>Fish/Rod/Lure/Distance/Global ????????????????????????????????????</t>
         </is>
       </c>
       <c r="F19" s="21" t="inlineStr">
@@ -6926,12 +6940,12 @@
       </c>
       <c r="G19" s="21" t="inlineStr">
         <is>
-          <t>补 Fish/Rod/Lure 数据表、重鱼生成条件和可配置验证入口。</t>
+          <t>????????????????</t>
         </is>
       </c>
       <c r="H19" s="21" t="inlineStr">
         <is>
-          <t>抽离数据表并加入重鱼条件。</t>
+          <t>???????????????</t>
         </is>
       </c>
     </row>
@@ -7074,17 +7088,17 @@
       </c>
       <c r="C23" s="34" t="inlineStr">
         <is>
-          <t>部分完成</t>
+          <t>????</t>
         </is>
       </c>
       <c r="D23" s="32" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>30%</t>
         </is>
       </c>
       <c r="E23" s="21" t="inlineStr">
         <is>
-          <t>FishGame UI 已可运行并能从主循环进入。</t>
+          <t>FishGame UI ?????????????????????????/??/?? Beam ??????????</t>
         </is>
       </c>
       <c r="F23" s="21" t="inlineStr">
@@ -7094,12 +7108,12 @@
       </c>
       <c r="G23" s="21" t="inlineStr">
         <is>
-          <t>缺第三人称角色动作占位、基础钓竿/浮漂/鱼线 Beam 等道具接入。</t>
+          <t>????????????????/??/?? Beam ??????</t>
         </is>
       </c>
       <c r="H23" s="21" t="inlineStr">
         <is>
-          <t>补角色动作与鱼线/浮漂可视化。</t>
+          <t>??????????????</t>
         </is>
       </c>
     </row>
@@ -7158,17 +7172,17 @@
       </c>
       <c r="C25" s="34" t="inlineStr">
         <is>
-          <t>部分完成</t>
+          <t>????</t>
         </is>
       </c>
       <c r="D25" s="32" t="inlineStr">
         <is>
-          <t>35%</t>
+          <t>45%</t>
         </is>
       </c>
       <c r="E25" s="21" t="inlineStr">
         <is>
-          <t>FishGame UI 预制体已完成，12 种鱼数据已定义。</t>
+          <t>FishGame UI ???????12 ??? 5 ?????????????/??/????????</t>
         </is>
       </c>
       <c r="F25" s="21" t="inlineStr">
@@ -7178,12 +7192,12 @@
       </c>
       <c r="G25" s="21" t="inlineStr">
         <is>
-          <t>缺 4-6 种可区分鱼模型或图标、鱼饵图标，以及咬钩/拉力/成功失败的素材化表现。</t>
+          <t>? 4-6 ?????????????????????????/??/???????</t>
         </is>
       </c>
       <c r="H25" s="21" t="inlineStr">
         <is>
-          <t>优先做 4-6 种可区分素材。</t>
+          <t>??? 4-6 ???????</t>
         </is>
       </c>
     </row>
@@ -7284,17 +7298,17 @@
       </c>
       <c r="C28" s="34" t="inlineStr">
         <is>
-          <t>部分完成</t>
+          <t>????</t>
         </is>
       </c>
       <c r="D28" s="32" t="inlineStr">
         <is>
-          <t>30%</t>
+          <t>40%</t>
         </is>
       </c>
       <c r="E28" s="21" t="inlineStr">
         <is>
-          <t>已有基础提示文案、失败提示和操作说明，但没有正式新手引导系统。</t>
+          <t>??????????????????/????????????????????????</t>
         </is>
       </c>
       <c r="F28" s="21" t="inlineStr">
@@ -7304,12 +7318,12 @@
       </c>
       <c r="G28" s="21" t="inlineStr">
         <is>
-          <t>补首钓引导流程、失败原因分层提示与边界场景文案。</t>
+          <t>????????????????????????</t>
         </is>
       </c>
       <c r="H28" s="21" t="inlineStr">
         <is>
-          <t>设计首钓引导与失败文案分层。</t>
+          <t>??????????????</t>
         </is>
       </c>
     </row>

--- a/XProject/Docs/Far_Cry_5_Fishing_Gantt_v2.xlsx
+++ b/XProject/Docs/Far_Cry_5_Fishing_Gantt_v2.xlsx
@@ -692,7 +692,7 @@
       </c>
       <c r="K6" s="20" t="inlineStr">
         <is>
-          <t>???</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="L6" s="21" t="inlineStr">
@@ -702,12 +702,12 @@
       </c>
       <c r="M6" s="21" t="inlineStr">
         <is>
-          <t>FishGamePresenterV2 ?????/??/??/??/??/???????????????45m ???????? UI ???</t>
+          <t>FishGamePresenterV2 已实现 Idle/Casting/Waiting/Fighting/AutoRetrieve 五状态机，搏鱼改为 Struggling/Resting 双状态行为机；超距上限 45m 自动快速收线回退；锁线机制（左键收线/右键锁线）已完善；UI 已接入运行时。</t>
         </is>
       </c>
       <c r="N6" s="21" t="inlineStr">
         <is>
-          <t>?????????? FishGame UI ???????/????????????????</t>
+          <t>鱼竿选择弹窗 UI 尚为占位（TODO），需补鱼竿选购流程；装备钓竿入口仍在 FishGame UI 内部，未推进到角色/武器轮盘。</t>
         </is>
       </c>
     </row>
@@ -757,17 +757,17 @@
       </c>
       <c r="L7" s="21" t="inlineStr">
         <is>
-          <t>40%</t>
+          <t>85%</t>
         </is>
       </c>
       <c r="M7" s="21" t="inlineStr">
         <is>
-          <t>已实现 12 种鱼定义、随机出鱼与鱼饵偏好加权；WaterCard 仅有“当前水域/河岸试钓区”文本展示。</t>
+          <t>已实现 12 种鱼定义、4 距离区间加权随机选鱼、鱼饵偏好标签匹配（1.35-2.2x）、鱼竿等级硬截断过滤；WaterCard 区域信息显示已有；当前无实际水域/河岸判定，仅靠距离分层替代。</t>
         </is>
       </c>
       <c r="N7" s="21" t="inlineStr">
         <is>
-          <t>补真实钓点配置、水域判定、场景钓点对象与首钓入口。</t>
+          <t>缺水域场景判定（当前仅距离分层），鱼种视觉素材全部缺失。</t>
         </is>
       </c>
     </row>
@@ -812,22 +812,22 @@
       </c>
       <c r="K8" s="22" t="inlineStr">
         <is>
-          <t>????</t>
+          <t>部分完成</t>
         </is>
       </c>
       <c r="L8" s="21" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>65%</t>
         </is>
       </c>
       <c r="M8" s="21" t="inlineStr">
         <is>
-          <t>FishGame ???? Gameplay ????? TripleMerge ?????FishGame ????????????? FishGame ????</t>
+          <t>FishGame 已注册为默认 Gameplay，可与 TripleMerge 双向异步切换；SaveFileFishGame 独立存档已完整接入（RodId/BaitId/OwnedBaits/FishBag/统计量），支持自动存档；Session 生命周期完整。</t>
         </is>
       </c>
       <c r="N8" s="21" t="inlineStr">
         <is>
-          <t>????????????/???????????????????</t>
+          <t>鱼获仍记录在 FishGame 内部列表，未接入主游戏背包/库存系统；鱼竿选择 UI 为 TODO 占位。</t>
         </is>
       </c>
     </row>
@@ -872,22 +872,22 @@
       </c>
       <c r="K9" s="22" t="inlineStr">
         <is>
-          <t>????</t>
+          <t>部分完成</t>
         </is>
       </c>
       <c r="L9" s="21" t="inlineStr">
         <is>
-          <t>70%</t>
+          <t>80%</t>
         </is>
       </c>
       <c r="M9" s="21" t="inlineStr">
         <is>
-          <t>???????????Coin ??????????????????????????????????????</t>
+          <t>一键全部出售已实现，通过 CurrencyModel.AddCurrency 统一入账 Coin；鱼饵购买（60-120 Coin/10 包）已完整接入；鱼竿价格已配置（0-500 Coin）但选购弹窗 UI 为 TODO。</t>
         </is>
       </c>
       <c r="N9" s="21" t="inlineStr">
         <is>
-          <t>??? UI/??????????????????????????</t>
+          <t>鱼竿选购 UI 待实现；无独立商贩/摊位入口，售卖仅在钓鱼 UI Idle 面板内。</t>
         </is>
       </c>
     </row>
@@ -932,7 +932,7 @@
       </c>
       <c r="K10" s="23" t="inlineStr">
         <is>
-          <t>未发现实现</t>
+          <t>未开始实现</t>
         </is>
       </c>
       <c r="L10" s="21" t="inlineStr">
@@ -942,12 +942,12 @@
       </c>
       <c r="M10" s="21" t="inlineStr">
         <is>
-          <t>仓库未检索到 Fisher King 或 Perk 对钓鱼疲劳参数的接入代码。</t>
+          <t>仓库中无任何 Perk 相关代码、配置或 UI，Fisher King 与疲劳减速机制均未涉及。</t>
         </is>
       </c>
       <c r="N10" s="21" t="inlineStr">
         <is>
-          <t>接入现有 Perk 系统，并让鱼竿疲劳倍率受配置驱动。</t>
+          <t>需从零设计并实现 Perk 系统框架、Fisher King 特技与疲劳衰减公式。</t>
         </is>
       </c>
     </row>
@@ -992,22 +992,22 @@
       </c>
       <c r="K11" s="22" t="inlineStr">
         <is>
-          <t>????</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="L11" s="21" t="inlineStr">
         <is>
-          <t>70%</t>
+          <t>90%</t>
         </is>
       </c>
       <c r="M11" s="21" t="inlineStr">
         <is>
-          <t>??? 5 ?????????????????????????????????????????????????</t>
+          <t>5 种鱼饵完整配置（3 消耗型 + 2 拟饵），切换按钮、库存追踪、消耗/无限区分、购买流程均已实现；鱼饵布局同步与基础飞蝇死局已修复；2 种拟饵通过 EnabledPhase=99 做阶段门控。</t>
         </is>
       </c>
       <c r="N11" s="21" t="inlineStr">
         <is>
-          <t>?????????????????????????? FishGame ???????</t>
+          <t>缺显式"未解锁"置灰 UI 与解锁来源提示；拟饵解锁条件暂为硬编码阶段值。</t>
         </is>
       </c>
     </row>
@@ -1052,22 +1052,22 @@
       </c>
       <c r="K12" s="22" t="inlineStr">
         <is>
-          <t>????</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="L12" s="21" t="inlineStr">
         <is>
-          <t>75%</t>
+          <t>90%</t>
         </is>
       </c>
       <c r="M12" s="21" t="inlineStr">
         <is>
-          <t>Fish/Rod/Lure/Distance/Global ????????????????????????????????????</t>
+          <t>Fish/Rod/Lure/Distance/Global 五类 JSON 配置表已建立，FishGameConfigManager 单例管理；12 种鱼含行为时长/冲刺概率/消耗恢复速率等完整参数；鱼竿独立配置含线强度/收线速度/控制力/压制力；鱼饵偏好权重可配。</t>
         </is>
       </c>
       <c r="N12" s="21" t="inlineStr">
         <is>
-          <t>???????????????????????????</t>
+          <t>缺配置可视化编辑器与数值平衡的自动化验证入口。</t>
         </is>
       </c>
     </row>
@@ -1112,7 +1112,7 @@
       </c>
       <c r="K13" s="23" t="inlineStr">
         <is>
-          <t>未发现实现</t>
+          <t>未开始实现</t>
         </is>
       </c>
       <c r="L13" s="21" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="M13" s="21" t="inlineStr">
         <is>
-          <t>未在运行时代码中检索到 Hard Fishing Spot、挑战鱼规则或硬钓点配置。</t>
+          <t>仓库中无任何 Hard Fishing Spot 相关代码或配置，无地点/区域系统。</t>
         </is>
       </c>
       <c r="N13" s="21" t="inlineStr">
         <is>
-          <t>先定义硬钓点数据结构，再接挑战鱼生成和场景标记。</t>
+          <t>需先定义硬核钓点数据结构与场景标识，再接入挑战生成逻辑与解锁条件。</t>
         </is>
       </c>
     </row>
@@ -1172,22 +1172,22 @@
       </c>
       <c r="K14" s="23" t="inlineStr">
         <is>
-          <t>未发现实现</t>
+          <t>未开始实现</t>
         </is>
       </c>
       <c r="L14" s="21" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>5%</t>
         </is>
       </c>
       <c r="M14" s="21" t="inlineStr">
         <is>
-          <t>未检索到区域纪录计算、纪录刷新逻辑或纪录板 UI。</t>
+          <t>FishBag 中有基础鱼获记录（FishId/Species/Rarity/Weight/SellPrice），TotalCaughtCount/TotalSoldCount 统计已有；但无物种收集完成度追踪，无图鉴 UI。</t>
         </is>
       </c>
       <c r="N14" s="21" t="inlineStr">
         <is>
-          <t>补纪录数据结构、刷新逻辑、展示 UI 和触发时机。</t>
+          <t>需设计图鉴数据结构（已捕获/未发现/稀有度标记），实现图鉴 UI 与刷新逻辑。</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="K15" s="23" t="inlineStr">
         <is>
-          <t>未发现实现</t>
+          <t>未开始实现</t>
         </is>
       </c>
       <c r="L15" s="21" t="inlineStr">
@@ -1242,12 +1242,12 @@
       </c>
       <c r="M15" s="21" t="inlineStr">
         <is>
-          <t>Old Betsy 只出现在 ThirdParty 参考脚本中，当前项目运行时代码未接入。</t>
+          <t>Old Betsy 仅存在于 ThirdParty 参考脚本中，当前项目代码内暂无任何收藏触发机制。</t>
         </is>
       </c>
       <c r="N15" s="21" t="inlineStr">
         <is>
-          <t>补解锁条件判定、发放逻辑、装备入口和终极鱼竿参数。</t>
+          <t>需设计收藏品判定条件、触发逻辑、装备入口与收藏品背包集成。</t>
         </is>
       </c>
     </row>
@@ -1296,22 +1296,22 @@
       </c>
       <c r="K16" s="22" t="inlineStr">
         <is>
-          <t>????</t>
+          <t>部分完成</t>
         </is>
       </c>
       <c r="L16" s="21" t="inlineStr">
         <is>
-          <t>30%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="M16" s="21" t="inlineStr">
         <is>
-          <t>FishGame UI ?????????????????????????/??/?? Beam ??????????</t>
+          <t>FishGame UI 面板已完整接入主循环，可从 Idle 进入完整钓鱼流程；但无第三人称角色钓鱼动画，无 R15 角色绑定，无抛竿/浮漂/鱼线 Beam 视觉表现。Boob1 角色为通用占位。</t>
         </is>
       </c>
       <c r="N16" s="21" t="inlineStr">
         <is>
-          <t>????????????????????????????</t>
+          <t>需接入钓鱼专用角色动画（抛竿/等待/搏鱼/收线/失败），补鱼线 Beam 与浮漂可视化。</t>
         </is>
       </c>
     </row>
@@ -1360,7 +1360,7 @@
       </c>
       <c r="K17" s="23" t="inlineStr">
         <is>
-          <t>未发现实现</t>
+          <t>未开始实现</t>
         </is>
       </c>
       <c r="L17" s="21" t="inlineStr">
@@ -1370,12 +1370,12 @@
       </c>
       <c r="M17" s="21" t="inlineStr">
         <is>
-          <t>未见装备/抛竿/等待/收线/上鱼/失败动画资源接入，也未见 P0 音效接线。</t>
+          <t>未有任何钓鱼相关动画资源或音效文件；AudioSysManager 音频系统已存在但 FishGame 零调用；whoosh/bite/reel/fail 等 P0 音效均未制作。</t>
         </is>
       </c>
       <c r="N17" s="21" t="inlineStr">
         <is>
-          <t>补动作占位和 whoosh/bite/reel/fail 等关键音效，先保证演示可读性。</t>
+          <t>需制作并接入抛竿/咬钩/收线/失败等关键音效，优先保证可听反馈覆盖核心状态变化。</t>
         </is>
       </c>
     </row>
@@ -1424,22 +1424,22 @@
       </c>
       <c r="K18" s="22" t="inlineStr">
         <is>
-          <t>????</t>
+          <t>部分完成</t>
         </is>
       </c>
       <c r="L18" s="21" t="inlineStr">
         <is>
-          <t>45%</t>
+          <t>40%</t>
         </is>
       </c>
       <c r="M18" s="21" t="inlineStr">
         <is>
-          <t>FishGame UI ???????12 ??? 5 ?????????????/??/????????</t>
+          <t>FishGameMainUI 预制体含 5 面板（Header/Hud/Status/Inventory/Controls），12 种鱼与 5 种鱼饵数据已定义；但无任何鱼模型/图标/鱼饵图标/鱼竿模型，无 FishGame 专用 SpriteAtlas。</t>
         </is>
       </c>
       <c r="N18" s="21" t="inlineStr">
         <is>
-          <t>? 4-6 ?????????????????????????/??/???????</t>
+          <t>需制作 4-6 种可区分鱼模型或图标、鱼饵图标，以及咬钩/拉力/成功失败的素材化表现。</t>
         </is>
       </c>
     </row>
@@ -1484,7 +1484,7 @@
       </c>
       <c r="K19" s="23" t="inlineStr">
         <is>
-          <t>未发现实现</t>
+          <t>未开始实现</t>
         </is>
       </c>
       <c r="L19" s="21" t="inlineStr">
@@ -1494,12 +1494,12 @@
       </c>
       <c r="M19" s="21" t="inlineStr">
         <is>
-          <t>未见水花/气泡/鱼跃提示、商贩摊位、纪录板视觉实现或场景件接入。</t>
+          <t>无水花/涟漪/跃鱼 VFX，无钓鱼场景 3D 环境（码头/水面/岸边），无商贩摊位，无图鉴 UI 视觉实现。</t>
         </is>
       </c>
       <c r="N19" s="21" t="inlineStr">
         <is>
-          <t>优先补钓点 VFX、Hard Spot 标识和纪录板视觉占位。</t>
+          <t>优先补基础水面 VFX 与 Hard Spot 场景标识，再做图鉴视觉占位。</t>
         </is>
       </c>
     </row>
@@ -1544,7 +1544,7 @@
       </c>
       <c r="K20" s="23" t="inlineStr">
         <is>
-          <t>未发现实现</t>
+          <t>未开始实现</t>
         </is>
       </c>
       <c r="L20" s="21" t="inlineStr">
@@ -1554,12 +1554,12 @@
       </c>
       <c r="M20" s="21" t="inlineStr">
         <is>
-          <t>未见 12 种鱼展示补齐、4 档鱼竿差异化、免费素材治理记录或 P1 音效增强。</t>
+          <t>未有 12 种鱼展示接入、4 种鱼饵差异化材质、素材包全面审查或 P1 音效增强。</t>
         </is>
       </c>
       <c r="N20" s="21" t="inlineStr">
         <is>
-          <t>进入上线阶段前补素材清理、性能检查和风格统一。</t>
+          <t>需在美术阶段前完成素材清单与美术规范统一，确保交付前资源可集成。</t>
         </is>
       </c>
     </row>
@@ -1632,22 +1632,22 @@
       </c>
       <c r="K22" s="22" t="inlineStr">
         <is>
-          <t>????</t>
+          <t>部分完成</t>
         </is>
       </c>
       <c r="L22" s="21" t="inlineStr">
         <is>
-          <t>40%</t>
+          <t>35%</t>
         </is>
       </c>
       <c r="M22" s="21" t="inlineStr">
         <is>
-          <t>??????????????????/????????????????????????</t>
+          <t>已有上下文通知系统（NotifyPanel）：抛竿提示、咬钩等待提示、搏鱼状态动态提示（挣扎/喘息/冲刺）与 ActionHint 操作引导，但无正式教程系统。</t>
         </is>
       </c>
       <c r="N22" s="21" t="inlineStr">
         <is>
-          <t>????????????????????????</t>
+          <t>缺首钓结构化引导流程、首次进入检测、步骤式教程 UI 与失败原因分层提示。</t>
         </is>
       </c>
     </row>
@@ -1692,7 +1692,7 @@
       </c>
       <c r="K23" s="23" t="inlineStr">
         <is>
-          <t>未发现实现</t>
+          <t>未开始实现</t>
         </is>
       </c>
       <c r="L23" s="21" t="inlineStr">
@@ -1702,12 +1702,12 @@
       </c>
       <c r="M23" s="21" t="inlineStr">
         <is>
-          <t>未检索到钓鱼相关埋点/Analytics；Assets 下也没有 FishGame 自动化测试。</t>
+          <t>仓库中无 FishGame 相关单元测试、集成测试或自动化回归，Assets 内也无 FishGame 测试目录。</t>
         </is>
       </c>
       <c r="N23" s="21" t="inlineStr">
         <is>
-          <t>补埋点、边界场景用例、回归测试与上线前 checklist。</t>
+          <t>需建立选鱼算法、体力/张力公式、状态转换与边界场景的自动化测试 checklist。</t>
         </is>
       </c>
     </row>
@@ -1766,22 +1766,22 @@
       <c r="J27" s="27" t="n"/>
       <c r="K27" s="26" t="inlineStr">
         <is>
-          <t>????</t>
+          <t>部分完成</t>
         </is>
       </c>
       <c r="L27" s="27" t="inlineStr">
         <is>
-          <t>75%</t>
+          <t>80%</t>
         </is>
       </c>
       <c r="M27" s="27" t="inlineStr">
         <is>
-          <t>?????????????????????? Coin???????????????????????</t>
+          <t>核心钓鱼全状态机、搏鱼双状态行为机、12 种鱼配置、经济闭环（Coin 入账/鱼饵购买/一键出售）、独立存档均已完整；鱼竿选购 UI 为 TODO，背包/库存未接入主游戏系统。</t>
         </is>
       </c>
       <c r="N27" s="27" t="inlineStr">
         <is>
-          <t>????????????????????? M1 ?????</t>
+          <t>补鱼竿选购弹窗与背包对接后即可视为 M1 真正闭环。</t>
         </is>
       </c>
     </row>
@@ -1810,22 +1810,22 @@
       <c r="J28" s="27" t="n"/>
       <c r="K28" s="26" t="inlineStr">
         <is>
-          <t>????</t>
+          <t>部分完成</t>
         </is>
       </c>
       <c r="L28" s="27" t="inlineStr">
         <is>
-          <t>45%</t>
+          <t>60%</t>
         </is>
       </c>
       <c r="M28" s="27" t="inlineStr">
         <is>
-          <t>????????????????????????????</t>
+          <t>鱼饵系统（5 种/切换/购买/库存）与五类配置表（Fish/Rod/Lure/Distance/Global）已基本完善；Perk 系统完全未实现。</t>
         </is>
       </c>
       <c r="N28" s="27" t="inlineStr">
         <is>
-          <t>Perk??????????????????????????????</t>
+          <t>Perk 系统为 M2 最大缺口，需从零设计并实现 Fisher King 与疲劳机制。</t>
         </is>
       </c>
     </row>
@@ -1854,7 +1854,7 @@
       <c r="J29" s="27" t="n"/>
       <c r="K29" s="28" t="inlineStr">
         <is>
-          <t>未发现实现</t>
+          <t>未开始实现</t>
         </is>
       </c>
       <c r="L29" s="27" t="inlineStr">
@@ -1864,12 +1864,12 @@
       </c>
       <c r="M29" s="27" t="inlineStr">
         <is>
-          <t>Hard Spot、纪录板、Old Betsy 三项均未在运行时代码中落地。</t>
+          <t>Hard Spot、图鉴册（仅有基础记录无 UI）、Old Betsy 收藏均未开始，暂无相关代码。</t>
         </is>
       </c>
       <c r="N29" s="27" t="inlineStr">
         <is>
-          <t>建议先做数据结构和 UI 占位，再串目标链。</t>
+          <t>需先定义硬核钓点数据结构与 UI 占位，再从目标功能切入。</t>
         </is>
       </c>
     </row>
@@ -1898,22 +1898,22 @@
       <c r="J30" s="27" t="n"/>
       <c r="K30" s="28" t="inlineStr">
         <is>
-          <t>未发现实现</t>
+          <t>未开始实现</t>
         </is>
       </c>
       <c r="L30" s="27" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>15%</t>
         </is>
       </c>
       <c r="M30" s="27" t="inlineStr">
         <is>
-          <t>埋点、边界、引导、数值与测试回归尚未形成上线项。</t>
+          <t>仅有上下文通知提示，无结构化引导、无自动化测试、无数值回归验证。</t>
         </is>
       </c>
       <c r="N30" s="27" t="inlineStr">
         <is>
-          <t>先补 QA 与数据层，再做数值打磨。</t>
+          <t>先建 QA 测试与数据层，再做引导与数值打磨。</t>
         </is>
       </c>
     </row>
@@ -6454,7 +6454,7 @@
     <row r="2" ht="36" customHeight="1" s="17">
       <c r="A2" s="30" t="inlineStr">
         <is>
-          <t>?????2026-03-27??????????????????????????? PRD ???????</t>
+          <t>更新日期：2026-03-28；评估口径：仅以当前仓库内已接入的代码与资源为准，不按 PRD 文案视为完成。</t>
         </is>
       </c>
       <c r="B2" s="18" t="n"/>
@@ -6510,7 +6510,7 @@
       </c>
       <c r="E5" s="21" t="inlineStr">
         <is>
-          <t>???????????/??/Coin/?????????????????????????</t>
+          <t>核心钓鱼全状态机已完成，鱼群/流程/经济均为部分完成；鱼竿选购 UI 和背包对接是主要缺口。</t>
         </is>
       </c>
     </row>
@@ -6521,17 +6521,17 @@
         </is>
       </c>
       <c r="B6" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="C6" s="32" t="n">
         <v>0</v>
-      </c>
-      <c r="C6" s="32" t="n">
-        <v>2</v>
       </c>
       <c r="D6" s="32" t="n">
         <v>1</v>
       </c>
       <c r="E6" s="21" t="inlineStr">
         <is>
-          <t>?????????????????????Perk ?????????</t>
+          <t>鱼饵系统与数值配置表已基本完善，Perk 系统完全未实现。</t>
         </is>
       </c>
     </row>
@@ -6552,7 +6552,7 @@
       </c>
       <c r="E7" s="21" t="inlineStr">
         <is>
-          <t>Hard Spot、纪录板、Old Betsy 均未落地。</t>
+          <t>Hard Spot、图鉴册、Old Betsy 均未开始，仅有基础鱼获记录。</t>
         </is>
       </c>
     </row>
@@ -6573,7 +6573,7 @@
       </c>
       <c r="E8" s="21" t="inlineStr">
         <is>
-          <t>目前以 UI/数据演示为主，资源与表现层缺口较大。</t>
+          <t>UI 框架与预制体已完成，但角色动画/音效/鱼模型/VFX/场景资源全面缺失。</t>
         </is>
       </c>
     </row>
@@ -6594,7 +6594,7 @@
       </c>
       <c r="E9" s="21" t="inlineStr">
         <is>
-          <t>??????????????????????????????</t>
+          <t>仅有上下文通知提示，无结构化引导与自动化测试。</t>
         </is>
       </c>
     </row>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="C13" s="33" t="inlineStr">
         <is>
-          <t>???</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="D13" s="32" t="inlineStr">
@@ -6678,7 +6678,7 @@
       </c>
       <c r="E13" s="21" t="inlineStr">
         <is>
-          <t>FishGamePresenterV2 ?????/??/??/??/??/???????????????45m ???????? UI ???</t>
+          <t>FishGamePresenterV2 五状态机完整，搏鱼 Struggling/Resting 双状态行为机、45m 失败距离、锁线机制均已实现；UI 已接入运行时。</t>
         </is>
       </c>
       <c r="F13" s="21" t="inlineStr">
@@ -6688,12 +6688,12 @@
       </c>
       <c r="G13" s="21" t="inlineStr">
         <is>
-          <t>?????????? FishGame UI ???????/?????</t>
+          <t>鱼竿选择弹窗为 TODO 占位；装备钓竿入口未推进到角色/武器轮盘。</t>
         </is>
       </c>
       <c r="H13" s="21" t="inlineStr">
         <is>
-          <t>?????? UI ???????/???????????????</t>
+          <t>补鱼竿选购弹窗 UI，推进装备入口到角色系统。</t>
         </is>
       </c>
     </row>
@@ -6715,12 +6715,12 @@
       </c>
       <c r="D14" s="32" t="inlineStr">
         <is>
-          <t>40%</t>
+          <t>85%</t>
         </is>
       </c>
       <c r="E14" s="21" t="inlineStr">
         <is>
-          <t>已实现 12 种鱼定义、随机出鱼与鱼饵偏好加权；WaterCard 仅有“当前水域/河岸试钓区”文本展示。</t>
+          <t>12 种鱼完整配置，4 距离区间加权随机选鱼，鱼饵偏好标签匹配，鱼竿等级硬截断过滤均已实现；无实际水域场景判定。</t>
         </is>
       </c>
       <c r="F14" s="21" t="inlineStr">
@@ -6730,12 +6730,12 @@
       </c>
       <c r="G14" s="21" t="inlineStr">
         <is>
-          <t>补真实钓点配置、水域判定、场景钓点对象与首钓入口。</t>
+          <t>缺水域场景判定，仅靠距离分层替代；鱼种视觉素材全缺。</t>
         </is>
       </c>
       <c r="H14" s="21" t="inlineStr">
         <is>
-          <t>先做 1 个真实可钓点与水域判定。</t>
+          <t>补水域场景标识与鱼种可视化素材。</t>
         </is>
       </c>
     </row>
@@ -6752,17 +6752,17 @@
       </c>
       <c r="C15" s="34" t="inlineStr">
         <is>
-          <t>????</t>
+          <t>部分完成</t>
         </is>
       </c>
       <c r="D15" s="32" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>65%</t>
         </is>
       </c>
       <c r="E15" s="21" t="inlineStr">
         <is>
-          <t>FishGame ???? Gameplay ????? TripleMerge ?????FishGame ????????????? FishGame ????</t>
+          <t>FishGame 注册为默认 Gameplay，可与 TripleMerge 双向异步切换；SaveFileFishGame 独立存档完整接入；Session 生命周期完整。</t>
         </is>
       </c>
       <c r="F15" s="21" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="G15" s="21" t="inlineStr">
         <is>
-          <t>????????????/????????????????</t>
+          <t>鱼获仍在内部列表，未接入主游戏背包/库存；鱼竿选择 UI 为 TODO。</t>
         </is>
       </c>
       <c r="H15" s="21" t="inlineStr">
         <is>
-          <t>??????/??????????</t>
+          <t>对接背包/库存系统，补鱼竿选购弹窗。</t>
         </is>
       </c>
     </row>
@@ -6794,17 +6794,17 @@
       </c>
       <c r="C16" s="34" t="inlineStr">
         <is>
-          <t>????</t>
+          <t>部分完成</t>
         </is>
       </c>
       <c r="D16" s="32" t="inlineStr">
         <is>
-          <t>70%</t>
+          <t>80%</t>
         </is>
       </c>
       <c r="E16" s="21" t="inlineStr">
         <is>
-          <t>???????????Coin ??????????????????????????????????????</t>
+          <t>一键全部出售通过 CurrencyModel.AddCurrency 入账 Coin；鱼饵购买（60-120 Coin/10 包）完整；鱼竿价格已配（0-500 Coin）但选购弹窗 UI 为 TODO。</t>
         </is>
       </c>
       <c r="F16" s="21" t="inlineStr">
@@ -6814,12 +6814,12 @@
       </c>
       <c r="G16" s="21" t="inlineStr">
         <is>
-          <t>??? UI??????????????????????</t>
+          <t>鱼竿选购 UI 待实现；售卖仅在 Idle 面板内，无独立商贩入口。</t>
         </is>
       </c>
       <c r="H16" s="21" t="inlineStr">
         <is>
-          <t>????????????????</t>
+          <t>补鱼竿选购弹窗，考虑增加独立商贩 UI。</t>
         </is>
       </c>
     </row>
@@ -6836,7 +6836,7 @@
       </c>
       <c r="C17" s="35" t="inlineStr">
         <is>
-          <t>未发现实现</t>
+          <t>未开始实现</t>
         </is>
       </c>
       <c r="D17" s="32" t="inlineStr">
@@ -6846,7 +6846,7 @@
       </c>
       <c r="E17" s="21" t="inlineStr">
         <is>
-          <t>仓库未检索到 Fisher King 或 Perk 对钓鱼疲劳参数的接入代码。</t>
+          <t>仓库中无任何 Perk 代码、配置或 UI，Fisher King 与疲劳减速均未涉及。</t>
         </is>
       </c>
       <c r="F17" s="21" t="inlineStr">
@@ -6856,12 +6856,12 @@
       </c>
       <c r="G17" s="21" t="inlineStr">
         <is>
-          <t>接入现有 Perk 系统，并让鱼竿疲劳倍率受配置驱动。</t>
+          <t>需从零设计 Perk 系统框架与疲劳衰减公式。</t>
         </is>
       </c>
       <c r="H17" s="21" t="inlineStr">
         <is>
-          <t>补 Fisher King 对疲劳倍率的驱动。</t>
+          <t>从 Fisher King 与疲劳倍率入手设计。</t>
         </is>
       </c>
     </row>
@@ -6878,17 +6878,17 @@
       </c>
       <c r="C18" s="34" t="inlineStr">
         <is>
-          <t>????</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="D18" s="32" t="inlineStr">
         <is>
-          <t>70%</t>
+          <t>90%</t>
         </is>
       </c>
       <c r="E18" s="21" t="inlineStr">
         <is>
-          <t>??? 5 ??????????????????????????????????????</t>
+          <t>5 种鱼饵完整配置（3 消耗型 + 2 拟饵），切换/库存/购买均已实现；鱼饵布局同步与飞蝇死局已修复。</t>
         </is>
       </c>
       <c r="F18" s="21" t="inlineStr">
@@ -6898,12 +6898,12 @@
       </c>
       <c r="G18" s="21" t="inlineStr">
         <is>
-          <t>????????????????????</t>
+          <t>缺显式未解锁置灰 UI 与解锁来源提示。</t>
         </is>
       </c>
       <c r="H18" s="21" t="inlineStr">
         <is>
-          <t>???????????????????</t>
+          <t>补未解锁置灰显示与解锁来源标记。</t>
         </is>
       </c>
     </row>
@@ -6920,17 +6920,17 @@
       </c>
       <c r="C19" s="34" t="inlineStr">
         <is>
-          <t>????</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="D19" s="32" t="inlineStr">
         <is>
-          <t>75%</t>
+          <t>90%</t>
         </is>
       </c>
       <c r="E19" s="21" t="inlineStr">
         <is>
-          <t>Fish/Rod/Lure/Distance/Global ????????????????????????????????????</t>
+          <t>Fish/Rod/Lure/Distance/Global 五类 JSON 配置表已建立，FishGameConfigManager 统一管理；12 种鱼含行为参数完整。</t>
         </is>
       </c>
       <c r="F19" s="21" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="G19" s="21" t="inlineStr">
         <is>
-          <t>????????????????</t>
+          <t>缺配置可视化编辑器与数值平衡自动验证。</t>
         </is>
       </c>
       <c r="H19" s="21" t="inlineStr">
         <is>
-          <t>???????????????</t>
+          <t>补数值平衡验证工具与配置编辑器。</t>
         </is>
       </c>
     </row>
@@ -6962,7 +6962,7 @@
       </c>
       <c r="C20" s="35" t="inlineStr">
         <is>
-          <t>未发现实现</t>
+          <t>未开始实现</t>
         </is>
       </c>
       <c r="D20" s="32" t="inlineStr">
@@ -6972,7 +6972,7 @@
       </c>
       <c r="E20" s="21" t="inlineStr">
         <is>
-          <t>未在运行时代码中检索到 Hard Fishing Spot、挑战鱼规则或硬钓点配置。</t>
+          <t>仓库中无 Hard Fishing Spot 相关代码或配置，无地点/区域系统。</t>
         </is>
       </c>
       <c r="F20" s="21" t="inlineStr">
@@ -6982,12 +6982,12 @@
       </c>
       <c r="G20" s="21" t="inlineStr">
         <is>
-          <t>先定义硬钓点数据结构，再接挑战鱼生成和场景标记。</t>
+          <t>需先定义硬核钓点数据结构与场景标识。</t>
         </is>
       </c>
       <c r="H20" s="21" t="inlineStr">
         <is>
-          <t>先做数据结构和场景标识。</t>
+          <t>设计硬核钓点数据结构与解锁条件。</t>
         </is>
       </c>
     </row>
@@ -7004,17 +7004,17 @@
       </c>
       <c r="C21" s="35" t="inlineStr">
         <is>
-          <t>未发现实现</t>
+          <t>未开始实现</t>
         </is>
       </c>
       <c r="D21" s="32" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>5%</t>
         </is>
       </c>
       <c r="E21" s="21" t="inlineStr">
         <is>
-          <t>未检索到区域纪录计算、纪录刷新逻辑或纪录板 UI。</t>
+          <t>FishBag 有基础鱼获记录（FishId/Weight/Rarity），但无物种收集完成度追踪，无图鉴 UI。</t>
         </is>
       </c>
       <c r="F21" s="21" t="inlineStr">
@@ -7024,12 +7024,12 @@
       </c>
       <c r="G21" s="21" t="inlineStr">
         <is>
-          <t>补纪录数据结构、刷新逻辑、展示 UI 和触发时机。</t>
+          <t>需设计图鉴数据结构与展示 UI，补刷新逻辑。</t>
         </is>
       </c>
       <c r="H21" s="21" t="inlineStr">
         <is>
-          <t>先做纪录数据和最小 UI 占位。</t>
+          <t>先定义图鉴数据，再做最小 UI 占位。</t>
         </is>
       </c>
     </row>
@@ -7046,7 +7046,7 @@
       </c>
       <c r="C22" s="35" t="inlineStr">
         <is>
-          <t>未发现实现</t>
+          <t>未开始实现</t>
         </is>
       </c>
       <c r="D22" s="32" t="inlineStr">
@@ -7056,7 +7056,7 @@
       </c>
       <c r="E22" s="21" t="inlineStr">
         <is>
-          <t>Old Betsy 只出现在 ThirdParty 参考脚本中，当前项目运行时代码未接入。</t>
+          <t>Old Betsy 仅存在于 ThirdParty 参考脚本中，当前项目暂无收藏触发机制。</t>
         </is>
       </c>
       <c r="F22" s="21" t="inlineStr">
@@ -7066,12 +7066,12 @@
       </c>
       <c r="G22" s="21" t="inlineStr">
         <is>
-          <t>补解锁条件判定、发放逻辑、装备入口和终极鱼竿参数。</t>
+          <t>需设计收藏品判定、触发逻辑与装备入口。</t>
         </is>
       </c>
       <c r="H22" s="21" t="inlineStr">
         <is>
-          <t>补条件判定和 Old Betsy 发放。</t>
+          <t>先确认收藏品判定条件与 Old Betsy 配置。</t>
         </is>
       </c>
     </row>
@@ -7088,17 +7088,17 @@
       </c>
       <c r="C23" s="34" t="inlineStr">
         <is>
-          <t>????</t>
+          <t>部分完成</t>
         </is>
       </c>
       <c r="D23" s="32" t="inlineStr">
         <is>
-          <t>30%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="E23" s="21" t="inlineStr">
         <is>
-          <t>FishGame UI ?????????????????????????/??/?? Beam ??????????</t>
+          <t>FishGame UI 面板已完整接入主循环；但无第三人称角色钓鱼动画、无 R15 绑定、无抛竿/浮漂/鱼线 Beam 视觉。Boob1 为通用占位。</t>
         </is>
       </c>
       <c r="F23" s="21" t="inlineStr">
@@ -7108,12 +7108,12 @@
       </c>
       <c r="G23" s="21" t="inlineStr">
         <is>
-          <t>????????????????/??/?? Beam ??????</t>
+          <t>缺钓鱼专用角色动画、抛竿/浮漂/鱼线 Beam 道具可视化。</t>
         </is>
       </c>
       <c r="H23" s="21" t="inlineStr">
         <is>
-          <t>??????????????</t>
+          <t>接入钓鱼角色动画与鱼线可视化。</t>
         </is>
       </c>
     </row>
@@ -7130,7 +7130,7 @@
       </c>
       <c r="C24" s="35" t="inlineStr">
         <is>
-          <t>未发现实现</t>
+          <t>未开始实现</t>
         </is>
       </c>
       <c r="D24" s="32" t="inlineStr">
@@ -7140,7 +7140,7 @@
       </c>
       <c r="E24" s="21" t="inlineStr">
         <is>
-          <t>未见装备/抛竿/等待/收线/上鱼/失败动画资源接入，也未见 P0 音效接线。</t>
+          <t>未有任何钓鱼动画资源或音效文件；AudioSysManager 存在但 FishGame 零调用。</t>
         </is>
       </c>
       <c r="F24" s="21" t="inlineStr">
@@ -7150,12 +7150,12 @@
       </c>
       <c r="G24" s="21" t="inlineStr">
         <is>
-          <t>补动作占位和 whoosh/bite/reel/fail 等关键音效，先保证演示可读性。</t>
+          <t>动画资源与音效文件完全缺失，需从零制作。</t>
         </is>
       </c>
       <c r="H24" s="21" t="inlineStr">
         <is>
-          <t>先接 P0 音效，再补占位动画。</t>
+          <t>先接入 P0 音效（whoosh/bite/reel/fail），再补动画占位。</t>
         </is>
       </c>
     </row>
@@ -7172,17 +7172,17 @@
       </c>
       <c r="C25" s="34" t="inlineStr">
         <is>
-          <t>????</t>
+          <t>部分完成</t>
         </is>
       </c>
       <c r="D25" s="32" t="inlineStr">
         <is>
-          <t>45%</t>
+          <t>40%</t>
         </is>
       </c>
       <c r="E25" s="21" t="inlineStr">
         <is>
-          <t>FishGame UI ???????12 ??? 5 ?????????????/??/????????</t>
+          <t>FishGameMainUI 预制体含 5 面板，12 种鱼与 5 种鱼饵数据已定义；但无鱼模型/图标/鱼饵图标/鱼竿模型，无 FishGame SpriteAtlas。</t>
         </is>
       </c>
       <c r="F25" s="21" t="inlineStr">
@@ -7192,12 +7192,12 @@
       </c>
       <c r="G25" s="21" t="inlineStr">
         <is>
-          <t>? 4-6 ?????????????????????????/??/???????</t>
+          <t>缺 4-6 种可区分鱼模型/图标、鱼饵图标，及咬钩/拉力/成功失败素材。</t>
         </is>
       </c>
       <c r="H25" s="21" t="inlineStr">
         <is>
-          <t>??? 4-6 ???????</t>
+          <t>优先制作 4-6 种可区分鱼模型素材。</t>
         </is>
       </c>
     </row>
@@ -7214,7 +7214,7 @@
       </c>
       <c r="C26" s="35" t="inlineStr">
         <is>
-          <t>未发现实现</t>
+          <t>未开始实现</t>
         </is>
       </c>
       <c r="D26" s="32" t="inlineStr">
@@ -7224,7 +7224,7 @@
       </c>
       <c r="E26" s="21" t="inlineStr">
         <is>
-          <t>未见水花/气泡/鱼跃提示、商贩摊位、纪录板视觉实现或场景件接入。</t>
+          <t>无水花/涟漪/跃鱼 VFX，无钓鱼场景 3D 环境，无商贩摊位，无图鉴 UI 视觉。</t>
         </is>
       </c>
       <c r="F26" s="21" t="inlineStr">
@@ -7234,12 +7234,12 @@
       </c>
       <c r="G26" s="21" t="inlineStr">
         <is>
-          <t>优先补钓点 VFX、Hard Spot 标识和纪录板视觉占位。</t>
+          <t>基础水面 VFX、场景环境、图鉴视觉均未开始。</t>
         </is>
       </c>
       <c r="H26" s="21" t="inlineStr">
         <is>
-          <t>先补钓点 VFX 和纪录板视觉稿。</t>
+          <t>先补基础水面 VFX 与图鉴视觉占位。</t>
         </is>
       </c>
     </row>
@@ -7256,7 +7256,7 @@
       </c>
       <c r="C27" s="35" t="inlineStr">
         <is>
-          <t>未发现实现</t>
+          <t>未开始实现</t>
         </is>
       </c>
       <c r="D27" s="32" t="inlineStr">
@@ -7266,7 +7266,7 @@
       </c>
       <c r="E27" s="21" t="inlineStr">
         <is>
-          <t>未见 12 种鱼展示补齐、4 档鱼竿差异化、免费素材治理记录或 P1 音效增强。</t>
+          <t>未有 12 种鱼展示接入、4 种鱼饵差异化材质、素材包全面审查或 P1 音效增强。</t>
         </is>
       </c>
       <c r="F27" s="21" t="inlineStr">
@@ -7276,12 +7276,12 @@
       </c>
       <c r="G27" s="21" t="inlineStr">
         <is>
-          <t>进入上线阶段前补素材清理、性能检查和风格统一。</t>
+          <t>需在美术阶段前完成素材清单与规范统一。</t>
         </is>
       </c>
       <c r="H27" s="21" t="inlineStr">
         <is>
-          <t>补免费素材清理记录与性能检查。</t>
+          <t>整理素材清单，制定统一美术规范。</t>
         </is>
       </c>
     </row>
@@ -7298,17 +7298,17 @@
       </c>
       <c r="C28" s="34" t="inlineStr">
         <is>
-          <t>????</t>
+          <t>部分完成</t>
         </is>
       </c>
       <c r="D28" s="32" t="inlineStr">
         <is>
-          <t>40%</t>
+          <t>35%</t>
         </is>
       </c>
       <c r="E28" s="21" t="inlineStr">
         <is>
-          <t>??????????????????/????????????????????????</t>
+          <t>已有上下文通知系统（NotifyPanel）：抛竿/咬钩/搏鱼动态提示与 ActionHint 操作引导，但无结构化教程系统。</t>
         </is>
       </c>
       <c r="F28" s="21" t="inlineStr">
@@ -7318,12 +7318,12 @@
       </c>
       <c r="G28" s="21" t="inlineStr">
         <is>
-          <t>????????????????????????</t>
+          <t>缺首钓结构化引导、首次进入检测与失败原因分层。</t>
         </is>
       </c>
       <c r="H28" s="21" t="inlineStr">
         <is>
-          <t>??????????????</t>
+          <t>设计首钓引导与失败文案分层提示。</t>
         </is>
       </c>
     </row>
@@ -7340,7 +7340,7 @@
       </c>
       <c r="C29" s="35" t="inlineStr">
         <is>
-          <t>未发现实现</t>
+          <t>未开始实现</t>
         </is>
       </c>
       <c r="D29" s="32" t="inlineStr">
@@ -7350,7 +7350,7 @@
       </c>
       <c r="E29" s="21" t="inlineStr">
         <is>
-          <t>未检索到钓鱼相关埋点/Analytics；Assets 下也没有 FishGame 自动化测试。</t>
+          <t>仓库中无 FishGame 相关测试，Assets 内无测试目录。</t>
         </is>
       </c>
       <c r="F29" s="21" t="inlineStr">
@@ -7360,12 +7360,12 @@
       </c>
       <c r="G29" s="21" t="inlineStr">
         <is>
-          <t>补埋点、边界场景用例、回归测试与上线前 checklist。</t>
+          <t>需建立选鱼、体力/张力、状态转换等自动化测试。</t>
         </is>
       </c>
       <c r="H29" s="21" t="inlineStr">
         <is>
-          <t>先建埋点清单，再补边界用例。</t>
+          <t>先建测试清单，再补核心算法测试。</t>
         </is>
       </c>
     </row>

--- a/XProject/Docs/Far_Cry_5_Fishing_Gantt_v2.xlsx
+++ b/XProject/Docs/Far_Cry_5_Fishing_Gantt_v2.xlsx
@@ -697,17 +697,17 @@
       </c>
       <c r="L6" s="21" t="inlineStr">
         <is>
-          <t>95%</t>
+          <t>98%</t>
         </is>
       </c>
       <c r="M6" s="21" t="inlineStr">
         <is>
-          <t>FishGamePresenterV2 已实现 Idle/Casting/Waiting/Fighting/AutoRetrieve 五状态机，搏鱼改为 Struggling/Resting 双状态行为机；超距上限 45m 自动快速收线回退；锁线机制（左键收线/右键锁线）已完善；UI 已接入运行时。</t>
+          <t>FishGamePresenterV2 已实现 Idle/Casting/Waiting/Fighting/AutoRetrieve 五状态机；搏鱼改为 Burst/Fatigue/Steady 三态行为机，冲刺期有进度上限与危险张力，疲劳期为最佳收线窗口；蓄力抛竿配合距离区间；超距 50m 自动快速收线；鱼竿选择弹窗已完成（FishRodSelectPopup），支持购买/装备/切换；锁线操作已移除，简化为持续按住收线松手卸压。UI 已接入运行时，界面颜色已统一（FishGameColors）。</t>
         </is>
       </c>
       <c r="N6" s="21" t="inlineStr">
         <is>
-          <t>鱼竿选择弹窗 UI 尚为占位（TODO），需补鱼竿选购流程；装备钓竿入口仍在 FishGame UI 内部，未推进到角色/武器轮盘。</t>
+          <t>装备钓竿入口仍在 FishGame UI 内部，未推进到角色/武器轮盘；鱼竿弹窗可进一步补充属性对比展示。</t>
         </is>
       </c>
     </row>
@@ -817,17 +817,17 @@
       </c>
       <c r="L8" s="21" t="inlineStr">
         <is>
-          <t>65%</t>
+          <t>70%</t>
         </is>
       </c>
       <c r="M8" s="21" t="inlineStr">
         <is>
-          <t>FishGame 已注册为默认 Gameplay，可与 TripleMerge 双向异步切换；SaveFileFishGame 独立存档已完整接入（RodId/BaitId/OwnedBaits/FishBag/统计量），支持自动存档；Session 生命周期完整。</t>
+          <t>FishGame 已注册为默认 Gameplay，可与 TripleMerge 双向异步切换；SaveFileFishGame 独立存档已完整接入（RodId/BaitId/OwnedBaits/FishBag/统计量），支持自动存档；Session 生命周期完整；鱼竿选择弹窗已实现，可从钓鱼界面直接购买/装备。</t>
         </is>
       </c>
       <c r="N8" s="21" t="inlineStr">
         <is>
-          <t>鱼获仍记录在 FishGame 内部列表，未接入主游戏背包/库存系统；鱼竿选择 UI 为 TODO 占位。</t>
+          <t>鱼获仍记录在 FishGame 内部列表，未接入主游戏背包/库存系统。</t>
         </is>
       </c>
     </row>
@@ -877,17 +877,17 @@
       </c>
       <c r="L9" s="21" t="inlineStr">
         <is>
-          <t>80%</t>
+          <t>90%</t>
         </is>
       </c>
       <c r="M9" s="21" t="inlineStr">
         <is>
-          <t>一键全部出售已实现，通过 CurrencyModel.AddCurrency 统一入账 Coin；鱼饵购买（60-120 Coin/10 包）已完整接入；鱼竿价格已配置（0-500 Coin）但选购弹窗 UI 为 TODO。</t>
+          <t>一键全部出售已实现，通过 CurrencyModel.AddCurrency 统一入账 Coin；鱼饵购买（60-120 Coin/10 包）已完整接入；鱼竿选购弹窗已实现（FishRodSelectPopup），支持价格展示、购买确认与装备切换，价格 0-500 Coin。</t>
         </is>
       </c>
       <c r="N9" s="21" t="inlineStr">
         <is>
-          <t>鱼竿选购 UI 待实现；无独立商贩/摊位入口，售卖仅在钓鱼 UI Idle 面板内。</t>
+          <t>无独立商贩/摊位入口，售卖与选购仅在钓鱼 UI 面板内。</t>
         </is>
       </c>
     </row>
@@ -1057,12 +1057,12 @@
       </c>
       <c r="L12" s="21" t="inlineStr">
         <is>
-          <t>90%</t>
+          <t>95%</t>
         </is>
       </c>
       <c r="M12" s="21" t="inlineStr">
         <is>
-          <t>Fish/Rod/Lure/Distance/Global 五类 JSON 配置表已建立，FishGameConfigManager 单例管理；12 种鱼含行为时长/冲刺概率/消耗恢复速率等完整参数；鱼竿独立配置含线强度/收线速度/控制力/压制力；鱼饵偏好权重可配。</t>
+          <t>Fish/Rod/Lure/Distance/Global 五类 JSON 配置表已建立，FishGameConfigManager 单例管理；12 种鱼含行为时长/冲刺概率/消耗恢复速率等完整参数；鱼竿独立配置含线强度/收线速度/控制力/压制力；鱼饵偏好权重可配；全局参数已抽取到 fishglobal.json，含 50+ 可调参数。</t>
         </is>
       </c>
       <c r="N12" s="21" t="inlineStr">
@@ -1637,12 +1637,12 @@
       </c>
       <c r="L22" s="21" t="inlineStr">
         <is>
-          <t>35%</t>
+          <t>40%</t>
         </is>
       </c>
       <c r="M22" s="21" t="inlineStr">
         <is>
-          <t>已有上下文通知系统（NotifyPanel）：抛竿提示、咬钩等待提示、搏鱼状态动态提示（挣扎/喘息/冲刺）与 ActionHint 操作引导，但无正式教程系统。</t>
+          <t>已有上下文通知系统（NotifyPanel）：抛竿提示、咬钩等待提示、搏鱼三态动态提示（冲刺危险/疲劳窗口/稳态策略）与 ActionHint 操作引导；颜色语义化（成功绿/警告黄/错误红/信息蓝）；但无正式教程系统。</t>
         </is>
       </c>
       <c r="N22" s="21" t="inlineStr">
@@ -1771,17 +1771,17 @@
       </c>
       <c r="L27" s="27" t="inlineStr">
         <is>
-          <t>80%</t>
+          <t>85%</t>
         </is>
       </c>
       <c r="M27" s="27" t="inlineStr">
         <is>
-          <t>核心钓鱼全状态机、搏鱼双状态行为机、12 种鱼配置、经济闭环（Coin 入账/鱼饵购买/一键出售）、独立存档均已完整；鱼竿选购 UI 为 TODO，背包/库存未接入主游戏系统。</t>
+          <t>核心钓鱼五状态机与三态搏鱼行为机已完整；鱼竿选购弹窗已实现（FishRodSelectPopup）；12 种鱼配置、经济闭环（Coin 入账/鱼饵购买/鱼竿购买/一键出售）、独立存档均已完整；蓄力抛竿与距离区间、界面颜色统一已完成。</t>
         </is>
       </c>
       <c r="N27" s="27" t="inlineStr">
         <is>
-          <t>补鱼竿选购弹窗与背包对接后即可视为 M1 真正闭环。</t>
+          <t>背包/库存未接入主游戏系统；无独立商贩入口；装备入口未推进到角色/武器轮盘。</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="M28" s="27" t="inlineStr">
         <is>
-          <t>鱼饵系统（5 种/切换/购买/库存）与五类配置表（Fish/Rod/Lure/Distance/Global）已基本完善；Perk 系统完全未实现。</t>
+          <t>鱼饵系统（5 种/切换/购买/库存）与五类配置表（Fish/Rod/Lure/Distance/Global）已基本完善，全局参数已参数化到 fishglobal.json；Perk 系统完全未实现。</t>
         </is>
       </c>
       <c r="N28" s="27" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L30" s="27" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>20%</t>
         </is>
       </c>
       <c r="M30" s="27" t="inlineStr">
         <is>
-          <t>仅有上下文通知提示，无结构化引导、无自动化测试、无数值回归验证。</t>
+          <t>上下文通知系统已增强（三态搏鱼提示、语义化颜色反馈），但无结构化引导、无自动化测试、无数值回归验证。</t>
         </is>
       </c>
       <c r="N30" s="27" t="inlineStr">
@@ -6454,7 +6454,7 @@
     <row r="2" ht="36" customHeight="1" s="17">
       <c r="A2" s="30" t="inlineStr">
         <is>
-          <t>更新日期：2026-03-28；评估口径：仅以当前仓库内已接入的代码与资源为准，不按 PRD 文案视为完成。</t>
+          <t>更新日期：2026-03-29；评估口径：仅以当前仓库内已接入的代码与资源为准，不按 PRD 文案视为完成。</t>
         </is>
       </c>
       <c r="B2" s="18" t="n"/>
@@ -6510,7 +6510,7 @@
       </c>
       <c r="E5" s="21" t="inlineStr">
         <is>
-          <t>核心钓鱼全状态机已完成，鱼群/流程/经济均为部分完成；鱼竿选购 UI 和背包对接是主要缺口。</t>
+          <t>核心钓鱼全状态机已完成（含三态搏鱼机制重构）；鱼竿选购弹窗已实现；鱼群/流程/经济均为部分完成；背包对接仍为主要缺口。</t>
         </is>
       </c>
     </row>
@@ -6594,7 +6594,7 @@
       </c>
       <c r="E9" s="21" t="inlineStr">
         <is>
-          <t>仅有上下文通知提示，无结构化引导与自动化测试。</t>
+          <t>上下文通知系统已增强（搏鱼三态提示与语义化颜色），无结构化引导与自动化测试。</t>
         </is>
       </c>
     </row>
@@ -6673,27 +6673,27 @@
       </c>
       <c r="D13" s="32" t="inlineStr">
         <is>
-          <t>95%</t>
+          <t>98%</t>
         </is>
       </c>
       <c r="E13" s="21" t="inlineStr">
         <is>
-          <t>FishGamePresenterV2 五状态机完整，搏鱼 Struggling/Resting 双状态行为机、45m 失败距离、锁线机制均已实现；UI 已接入运行时。</t>
+          <t>FishGamePresenterV2 五状态机完整；搏鱼改为 Burst/Fatigue/Steady 三态行为机（冲刺进度上限+危险张力、疲劳最佳窗口、稳态渐进）；蓄力抛竿配合距离区间；超距 50m 自动快速收线；鱼竿选择弹窗已完成（FishRodSelectPopup），支持购买/装备/切换；锁线操作已移除；UI 已接入运行时，界面颜色统一。</t>
         </is>
       </c>
       <c r="F13" s="21" t="inlineStr">
         <is>
-          <t>装备钓竿、抛竿、咬钩、遛鱼、上鱼状态机</t>
+          <t>装备钓竿、抛竿、咬钩、遛鱼、上鱼状态机、鱼竿选购弹窗</t>
         </is>
       </c>
       <c r="G13" s="21" t="inlineStr">
         <is>
-          <t>鱼竿选择弹窗为 TODO 占位；装备钓竿入口未推进到角色/武器轮盘。</t>
+          <t>装备钓竿入口仍在 FishGame UI 内部，未推进到角色/武器轮盘。</t>
         </is>
       </c>
       <c r="H13" s="21" t="inlineStr">
         <is>
-          <t>补鱼竿选购弹窗 UI，推进装备入口到角色系统。</t>
+          <t>推进装备入口到角色系统，补鱼竿属性对比展示。</t>
         </is>
       </c>
     </row>
@@ -6757,12 +6757,12 @@
       </c>
       <c r="D15" s="32" t="inlineStr">
         <is>
-          <t>65%</t>
+          <t>70%</t>
         </is>
       </c>
       <c r="E15" s="21" t="inlineStr">
         <is>
-          <t>FishGame 注册为默认 Gameplay，可与 TripleMerge 双向异步切换；SaveFileFishGame 独立存档完整接入；Session 生命周期完整。</t>
+          <t>FishGame 注册为默认 Gameplay，可与 TripleMerge 双向异步切换；SaveFileFishGame 独立存档完整接入；Session 生命周期完整；鱼竿选择弹窗已实现。</t>
         </is>
       </c>
       <c r="F15" s="21" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="G15" s="21" t="inlineStr">
         <is>
-          <t>鱼获仍在内部列表，未接入主游戏背包/库存；鱼竿选择 UI 为 TODO。</t>
+          <t>鱼获仍在内部列表，未接入主游戏背包/库存系统。</t>
         </is>
       </c>
       <c r="H15" s="21" t="inlineStr">
         <is>
-          <t>对接背包/库存系统，补鱼竿选购弹窗。</t>
+          <t>对接背包/库存系统。</t>
         </is>
       </c>
     </row>
@@ -6799,12 +6799,12 @@
       </c>
       <c r="D16" s="32" t="inlineStr">
         <is>
-          <t>80%</t>
+          <t>90%</t>
         </is>
       </c>
       <c r="E16" s="21" t="inlineStr">
         <is>
-          <t>一键全部出售通过 CurrencyModel.AddCurrency 入账 Coin；鱼饵购买（60-120 Coin/10 包）完整；鱼竿价格已配（0-500 Coin）但选购弹窗 UI 为 TODO。</t>
+          <t>一键全部出售通过 CurrencyModel.AddCurrency 入账 Coin；鱼饵购买（60-120 Coin/10 包）完整；鱼竿选购弹窗已实现（FishRodSelectPopup），支持价格展示、购买确认与装备切换。</t>
         </is>
       </c>
       <c r="F16" s="21" t="inlineStr">
@@ -6814,12 +6814,12 @@
       </c>
       <c r="G16" s="21" t="inlineStr">
         <is>
-          <t>鱼竿选购 UI 待实现；售卖仅在 Idle 面板内，无独立商贩入口。</t>
+          <t>售卖与选购仅在 Idle 面板内，无独立商贩入口。</t>
         </is>
       </c>
       <c r="H16" s="21" t="inlineStr">
         <is>
-          <t>补鱼竿选购弹窗，考虑增加独立商贩 UI。</t>
+          <t>考虑增加独立商贩 UI 或与主游戏商店对接。</t>
         </is>
       </c>
     </row>
@@ -6925,12 +6925,12 @@
       </c>
       <c r="D19" s="32" t="inlineStr">
         <is>
-          <t>90%</t>
+          <t>95%</t>
         </is>
       </c>
       <c r="E19" s="21" t="inlineStr">
         <is>
-          <t>Fish/Rod/Lure/Distance/Global 五类 JSON 配置表已建立，FishGameConfigManager 统一管理；12 种鱼含行为参数完整。</t>
+          <t>Fish/Rod/Lure/Distance/Global 五类 JSON 配置表已建立，FishGameConfigManager 统一管理；12 种鱼含行为参数完整；全局参数已抽取到 fishglobal.json，含 50+ 可调参数。</t>
         </is>
       </c>
       <c r="F19" s="21" t="inlineStr">
@@ -7303,12 +7303,12 @@
       </c>
       <c r="D28" s="32" t="inlineStr">
         <is>
-          <t>35%</t>
+          <t>40%</t>
         </is>
       </c>
       <c r="E28" s="21" t="inlineStr">
         <is>
-          <t>已有上下文通知系统（NotifyPanel）：抛竿/咬钩/搏鱼动态提示与 ActionHint 操作引导，但无结构化教程系统。</t>
+          <t>已有上下文通知系统（NotifyPanel）：搏鱼三态动态提示（冲刺危险/疲劳窗口/稳态策略）与 ActionHint 操作引导；颜色语义化反馈；但无结构化教程系统。</t>
         </is>
       </c>
       <c r="F28" s="21" t="inlineStr">
